--- a/knowledge-source/FAQ库.xlsx
+++ b/knowledge-source/FAQ库.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F964DA7-ABAE-4CAE-BDD3-4127CB368D43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCB09FFF-4FA0-48B4-8DF9-3F9CB015DE9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="feature_faq" sheetId="2" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5468" uniqueCount="2740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5481" uniqueCount="2746">
   <si>
     <t>一级分类</t>
   </si>
@@ -6394,10 +6394,10 @@
     <t>extension_upload,permission_denied,extension_access</t>
   </si>
   <si>
-    <t>为什么我无法上传扩展？</t>
-  </si>
-  <si>
-    <t>Why can't I upload an extension?</t>
+    <t>为什么我无法在浏览器上传扩展？</t>
+  </si>
+  <si>
+    <t>Why can't I upload an extension in browser?</t>
   </si>
   <si>
     <t>1. Why can't I add extensions?
@@ -6448,6 +6448,28 @@
   </si>
   <si>
     <t>ERR-EXTADD-002</t>
+  </si>
+  <si>
+    <t>extension_upload_failed,upload_error,extension_management,extension_installation_package,network_issue</t>
+  </si>
+  <si>
+    <t>为什么在APP上传扩展时显示“上传失败”？</t>
+  </si>
+  <si>
+    <t>Why does extension upload fail in APP?</t>
+  </si>
+  <si>
+    <t>1. Why does my extension upload fail? 
+2. What should I do if DICloak shows an upload error when uploading an extension? 
+3. Why can’t I upload an extension installation package? 
+4. Is extension upload failure related to network issues? 
+5. How can I fix an extension upload error?</t>
+  </si>
+  <si>
+    <t>If an “Upload error” appears when uploading an extension package in extension management, it is usually related to an unstable network connection or a failed interface request. Restart the DICloak application first, then upload the extension package again. If the upload still fails, please send the installation package to customer support for further analysis.</t>
+  </si>
+  <si>
+    <t>ERR-EXTADD-003</t>
   </si>
   <si>
     <t>内核问题</t>
@@ -8290,7 +8312,8 @@
     <t>1.I was denied access to [tool] 
 2.[tool] is not working
 3.ToolSuite is not activated 
-4.I can't use [tool]</t>
+4.I can't use [tool]
+5.can't use chatgpt</t>
   </si>
   <si>
     <t>ROUTING-USAGE-006</t>
@@ -9538,7 +9561,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1FF546F-A870-4152-BEDA-AC3BB1A3E195}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D47EB84E-096A-4705-9B4A-ED132D3243F1}">
   <dimension ref="A1:U218"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -22515,8 +22538,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17350741-ED0B-433A-AA5B-CFAF03F2F53F}">
-  <dimension ref="A1:U59"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DEBEC25C-2C18-479C-9ADE-075FD333BDC7}">
+  <dimension ref="A1:U60"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="14" width="19" customWidth="1"/>
@@ -23541,7 +23564,7 @@
         <v>1806</v>
       </c>
       <c r="E19" t="s">
-        <v>46</v>
+        <v>131</v>
       </c>
       <c r="F19" t="s">
         <v>1807</v>
@@ -23580,7 +23603,7 @@
         <v>1814</v>
       </c>
       <c r="S19" s="2">
-        <v>46153.823877314811</v>
+        <v>46268.690092592595</v>
       </c>
       <c r="T19" s="2">
         <v>46135.87939814815</v>
@@ -23603,7 +23626,7 @@
         <v>1816</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F20" t="s">
         <v>1817</v>
@@ -23639,7 +23662,7 @@
         <v>1823</v>
       </c>
       <c r="S20" s="2">
-        <v>46155.651053240741</v>
+        <v>46268.690069444441</v>
       </c>
       <c r="T20" s="2">
         <v>46136.641863425924</v>
@@ -23662,7 +23685,7 @@
         <v>1825</v>
       </c>
       <c r="E21" t="s">
-        <v>46</v>
+        <v>251</v>
       </c>
       <c r="F21" t="s">
         <v>1826</v>
@@ -23689,7 +23712,7 @@
         <v>1829</v>
       </c>
       <c r="S21" s="2">
-        <v>46151.816874999997</v>
+        <v>46268.690185185187</v>
       </c>
       <c r="T21" s="2">
         <v>46151.81144675926</v>
@@ -23815,7 +23838,7 @@
         <v>1844</v>
       </c>
       <c r="E24" t="s">
-        <v>25</v>
+        <v>251</v>
       </c>
       <c r="F24" t="s">
         <v>1845</v>
@@ -23848,7 +23871,7 @@
         <v>1850</v>
       </c>
       <c r="S24" s="2">
-        <v>46262.776053240741</v>
+        <v>46268.690439814818</v>
       </c>
       <c r="T24" s="2">
         <v>46261.656134259261</v>
@@ -24216,7 +24239,7 @@
         <v>1902</v>
       </c>
       <c r="S31" s="2">
-        <v>46151.609282407408</v>
+        <v>46268.662731481483</v>
       </c>
       <c r="T31" s="2">
         <v>46133.616041666668</v>
@@ -24289,28 +24312,25 @@
         <v>1671</v>
       </c>
       <c r="B33" t="s">
+        <v>1015</v>
+      </c>
+      <c r="C33" t="s">
         <v>1912</v>
       </c>
-      <c r="C33" t="s">
+      <c r="D33" t="s">
         <v>1913</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
+        <v>25</v>
+      </c>
+      <c r="F33" t="s">
         <v>1914</v>
       </c>
-      <c r="E33" t="s">
-        <v>46</v>
-      </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>1915</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>1916</v>
-      </c>
-      <c r="I33" t="s">
-        <v>1917</v>
-      </c>
-      <c r="J33" t="s">
-        <v>1918</v>
       </c>
       <c r="N33" t="s">
         <v>52</v>
@@ -24319,22 +24339,22 @@
         <v>1681</v>
       </c>
       <c r="P33" t="s">
-        <v>1919</v>
+        <v>1023</v>
       </c>
       <c r="Q33" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="R33" t="s">
-        <v>1920</v>
+        <v>1917</v>
       </c>
       <c r="S33" s="2">
-        <v>46135.894305555557</v>
+        <v>46268.664537037039</v>
       </c>
       <c r="T33" s="2">
-        <v>46133.616041666668</v>
+        <v>46268.661979166667</v>
       </c>
       <c r="U33">
-        <v>17</v>
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="25.5" customHeight="1">
@@ -24342,25 +24362,28 @@
         <v>1671</v>
       </c>
       <c r="B34" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="C34" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E34" t="s">
+        <v>46</v>
+      </c>
+      <c r="F34" t="s">
         <v>1921</v>
       </c>
-      <c r="D34" t="s">
+      <c r="G34" t="s">
         <v>1922</v>
       </c>
-      <c r="E34" t="s">
-        <v>25</v>
-      </c>
-      <c r="F34" t="s">
+      <c r="I34" t="s">
         <v>1923</v>
       </c>
-      <c r="G34" t="s">
+      <c r="J34" t="s">
         <v>1924</v>
-      </c>
-      <c r="H34" t="s">
-        <v>1925</v>
       </c>
       <c r="N34" t="s">
         <v>52</v>
@@ -24369,22 +24392,22 @@
         <v>1681</v>
       </c>
       <c r="P34" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
       <c r="Q34" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R34" t="s">
         <v>1926</v>
       </c>
       <c r="S34" s="2">
-        <v>46133.839398148149</v>
+        <v>46135.894305555557</v>
       </c>
       <c r="T34" s="2">
         <v>46133.616041666668</v>
       </c>
       <c r="U34">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="25.5" customHeight="1">
@@ -24392,7 +24415,7 @@
         <v>1671</v>
       </c>
       <c r="B35" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="C35" t="s">
         <v>1927</v>
@@ -24419,22 +24442,22 @@
         <v>1681</v>
       </c>
       <c r="P35" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
       <c r="Q35" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R35" t="s">
         <v>1932</v>
       </c>
       <c r="S35" s="2">
-        <v>46142.649641203701</v>
+        <v>46133.839398148149</v>
       </c>
       <c r="T35" s="2">
         <v>46133.616041666668</v>
       </c>
       <c r="U35">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="25.5" customHeight="1">
@@ -24442,7 +24465,7 @@
         <v>1671</v>
       </c>
       <c r="B36" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="C36" t="s">
         <v>1933</v>
@@ -24451,7 +24474,7 @@
         <v>1934</v>
       </c>
       <c r="E36" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F36" t="s">
         <v>1935</v>
@@ -24462,12 +24485,6 @@
       <c r="H36" t="s">
         <v>1937</v>
       </c>
-      <c r="L36" t="s">
-        <v>1775</v>
-      </c>
-      <c r="M36" t="s">
-        <v>1776</v>
-      </c>
       <c r="N36" t="s">
         <v>52</v>
       </c>
@@ -24475,22 +24492,22 @@
         <v>1681</v>
       </c>
       <c r="P36" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
       <c r="Q36" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="R36" t="s">
         <v>1938</v>
       </c>
       <c r="S36" s="2">
-        <v>46267.758206018516</v>
+        <v>46142.649641203701</v>
       </c>
       <c r="T36" s="2">
         <v>46133.616041666668</v>
       </c>
       <c r="U36">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="37" spans="1:21" ht="25.5" customHeight="1">
@@ -24498,7 +24515,7 @@
         <v>1671</v>
       </c>
       <c r="B37" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="C37" t="s">
         <v>1939</v>
@@ -24507,7 +24524,7 @@
         <v>1940</v>
       </c>
       <c r="E37" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F37" t="s">
         <v>1941</v>
@@ -24515,11 +24532,14 @@
       <c r="G37" t="s">
         <v>1942</v>
       </c>
-      <c r="I37" t="s">
+      <c r="H37" t="s">
         <v>1943</v>
       </c>
-      <c r="J37" t="s">
-        <v>1944</v>
+      <c r="L37" t="s">
+        <v>1775</v>
+      </c>
+      <c r="M37" t="s">
+        <v>1776</v>
       </c>
       <c r="N37" t="s">
         <v>52</v>
@@ -24528,22 +24548,22 @@
         <v>1681</v>
       </c>
       <c r="P37" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
       <c r="Q37" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="R37" t="s">
-        <v>1945</v>
+        <v>1944</v>
       </c>
       <c r="S37" s="2">
-        <v>46135.896805555552</v>
+        <v>46267.758206018516</v>
       </c>
       <c r="T37" s="2">
-        <v>46135.894375000003</v>
+        <v>46133.616041666668</v>
       </c>
       <c r="U37">
-        <v>32</v>
+        <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:21" ht="25.5" customHeight="1">
@@ -24551,28 +24571,28 @@
         <v>1671</v>
       </c>
       <c r="B38" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1945</v>
+      </c>
+      <c r="D38" t="s">
         <v>1946</v>
-      </c>
-      <c r="C38" t="s">
-        <v>1947</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1948</v>
       </c>
       <c r="E38" t="s">
         <v>25</v>
       </c>
       <c r="F38" t="s">
+        <v>1947</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1948</v>
+      </c>
+      <c r="I38" t="s">
         <v>1949</v>
       </c>
-      <c r="G38" t="s">
+      <c r="J38" t="s">
         <v>1950</v>
-      </c>
-      <c r="I38" t="s">
-        <v>1951</v>
-      </c>
-      <c r="J38" t="s">
-        <v>1709</v>
       </c>
       <c r="N38" t="s">
         <v>52</v>
@@ -24581,22 +24601,22 @@
         <v>1681</v>
       </c>
       <c r="P38" t="s">
-        <v>1952</v>
+        <v>1925</v>
       </c>
       <c r="Q38" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="R38" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="S38" s="2">
-        <v>46149.833090277774</v>
+        <v>46135.896805555552</v>
       </c>
       <c r="T38" s="2">
-        <v>46133.616041666668</v>
+        <v>46135.894375000003</v>
       </c>
       <c r="U38">
-        <v>4</v>
+        <v>32</v>
       </c>
     </row>
     <row r="39" spans="1:21" ht="25.5" customHeight="1">
@@ -24604,25 +24624,28 @@
         <v>1671</v>
       </c>
       <c r="B39" t="s">
-        <v>1946</v>
+        <v>1952</v>
       </c>
       <c r="C39" t="s">
+        <v>1953</v>
+      </c>
+      <c r="D39" t="s">
         <v>1954</v>
       </c>
-      <c r="D39" t="s">
+      <c r="E39" t="s">
+        <v>25</v>
+      </c>
+      <c r="F39" t="s">
         <v>1955</v>
       </c>
-      <c r="E39" t="s">
-        <v>46</v>
-      </c>
-      <c r="F39" t="s">
+      <c r="G39" t="s">
         <v>1956</v>
       </c>
-      <c r="G39" t="s">
+      <c r="I39" t="s">
         <v>1957</v>
       </c>
-      <c r="H39" t="s">
-        <v>1958</v>
+      <c r="J39" t="s">
+        <v>1709</v>
       </c>
       <c r="N39" t="s">
         <v>52</v>
@@ -24631,22 +24654,22 @@
         <v>1681</v>
       </c>
       <c r="P39" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="Q39" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R39" t="s">
         <v>1959</v>
       </c>
       <c r="S39" s="2">
-        <v>46148.803032407406</v>
+        <v>46149.833090277774</v>
       </c>
       <c r="T39" s="2">
-        <v>46142.865856481483</v>
+        <v>46133.616041666668</v>
       </c>
       <c r="U39">
-        <v>41</v>
+        <v>4</v>
       </c>
     </row>
     <row r="40" spans="1:21" ht="25.5" customHeight="1">
@@ -24654,7 +24677,7 @@
         <v>1671</v>
       </c>
       <c r="B40" t="s">
-        <v>1946</v>
+        <v>1952</v>
       </c>
       <c r="C40" t="s">
         <v>1960</v>
@@ -24663,7 +24686,7 @@
         <v>1961</v>
       </c>
       <c r="E40" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F40" t="s">
         <v>1962</v>
@@ -24674,9 +24697,6 @@
       <c r="H40" t="s">
         <v>1964</v>
       </c>
-      <c r="I40" t="s">
-        <v>514</v>
-      </c>
       <c r="N40" t="s">
         <v>52</v>
       </c>
@@ -24684,22 +24704,22 @@
         <v>1681</v>
       </c>
       <c r="P40" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="Q40" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R40" t="s">
         <v>1965</v>
       </c>
       <c r="S40" s="2">
-        <v>46162.747349537036</v>
+        <v>46148.803032407406</v>
       </c>
       <c r="T40" s="2">
-        <v>46162.744409722225</v>
+        <v>46142.865856481483</v>
       </c>
       <c r="U40">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="41" spans="1:21" ht="25.5" customHeight="1">
@@ -24707,25 +24727,28 @@
         <v>1671</v>
       </c>
       <c r="B41" t="s">
+        <v>1952</v>
+      </c>
+      <c r="C41" t="s">
         <v>1966</v>
       </c>
-      <c r="C41" t="s">
+      <c r="D41" t="s">
         <v>1967</v>
       </c>
-      <c r="D41" t="s">
+      <c r="E41" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" t="s">
         <v>1968</v>
       </c>
-      <c r="E41" t="s">
-        <v>131</v>
-      </c>
-      <c r="F41" t="s">
+      <c r="G41" t="s">
         <v>1969</v>
       </c>
-      <c r="G41" t="s">
+      <c r="H41" t="s">
         <v>1970</v>
       </c>
-      <c r="H41" t="s">
-        <v>1971</v>
+      <c r="I41" t="s">
+        <v>514</v>
       </c>
       <c r="N41" t="s">
         <v>52</v>
@@ -24734,22 +24757,22 @@
         <v>1681</v>
       </c>
       <c r="P41" t="s">
-        <v>1972</v>
+        <v>1958</v>
       </c>
       <c r="Q41" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="R41" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="S41" s="2">
-        <v>46156.70857638889</v>
+        <v>46162.747349537036</v>
       </c>
       <c r="T41" s="2">
-        <v>46133.616041666668</v>
+        <v>46162.744409722225</v>
       </c>
       <c r="U41">
-        <v>23</v>
+        <v>59</v>
       </c>
     </row>
     <row r="42" spans="1:21" ht="25.5" customHeight="1">
@@ -24757,25 +24780,25 @@
         <v>1671</v>
       </c>
       <c r="B42" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="C42" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D42" t="s">
         <v>1974</v>
-      </c>
-      <c r="D42" t="s">
-        <v>1975</v>
       </c>
       <c r="E42" t="s">
         <v>131</v>
       </c>
       <c r="F42" t="s">
+        <v>1975</v>
+      </c>
+      <c r="G42" t="s">
         <v>1976</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
         <v>1977</v>
-      </c>
-      <c r="H42" t="s">
-        <v>1978</v>
       </c>
       <c r="N42" t="s">
         <v>52</v>
@@ -24784,22 +24807,22 @@
         <v>1681</v>
       </c>
       <c r="P42" t="s">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="Q42" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R42" t="s">
         <v>1979</v>
       </c>
       <c r="S42" s="2">
-        <v>46136.71738425926</v>
+        <v>46156.70857638889</v>
       </c>
       <c r="T42" s="2">
-        <v>46136.713761574072</v>
+        <v>46133.616041666668</v>
       </c>
       <c r="U42">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="43" spans="1:21" ht="25.5" customHeight="1">
@@ -24807,7 +24830,7 @@
         <v>1671</v>
       </c>
       <c r="B43" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="C43" t="s">
         <v>1980</v>
@@ -24816,7 +24839,7 @@
         <v>1981</v>
       </c>
       <c r="E43" t="s">
-        <v>25</v>
+        <v>131</v>
       </c>
       <c r="F43" t="s">
         <v>1982</v>
@@ -24834,22 +24857,22 @@
         <v>1681</v>
       </c>
       <c r="P43" t="s">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="Q43" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R43" t="s">
         <v>1985</v>
       </c>
       <c r="S43" s="2">
-        <v>46157.713356481479</v>
+        <v>46136.71738425926</v>
       </c>
       <c r="T43" s="2">
-        <v>46157.711585648147</v>
+        <v>46136.713761574072</v>
       </c>
       <c r="U43">
-        <v>52</v>
+        <v>38</v>
       </c>
     </row>
     <row r="44" spans="1:21" ht="25.5" customHeight="1">
@@ -24857,7 +24880,7 @@
         <v>1671</v>
       </c>
       <c r="B44" t="s">
-        <v>862</v>
+        <v>1972</v>
       </c>
       <c r="C44" t="s">
         <v>1986</v>
@@ -24866,7 +24889,7 @@
         <v>1987</v>
       </c>
       <c r="E44" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F44" t="s">
         <v>1988</v>
@@ -24874,20 +24897,8 @@
       <c r="G44" t="s">
         <v>1989</v>
       </c>
-      <c r="I44" t="s">
+      <c r="H44" t="s">
         <v>1990</v>
-      </c>
-      <c r="J44" t="s">
-        <v>1709</v>
-      </c>
-      <c r="K44" t="s">
-        <v>1991</v>
-      </c>
-      <c r="L44" t="s">
-        <v>1992</v>
-      </c>
-      <c r="M44" t="s">
-        <v>1993</v>
       </c>
       <c r="N44" t="s">
         <v>52</v>
@@ -24896,22 +24907,22 @@
         <v>1681</v>
       </c>
       <c r="P44" t="s">
-        <v>870</v>
+        <v>1978</v>
       </c>
       <c r="Q44" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="R44" t="s">
-        <v>1994</v>
+        <v>1991</v>
       </c>
       <c r="S44" s="2">
-        <v>46154.834027777775</v>
+        <v>46157.713356481479</v>
       </c>
       <c r="T44" s="2">
-        <v>46154.814571759256</v>
+        <v>46157.711585648147</v>
       </c>
       <c r="U44">
-        <v>44</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:21" ht="25.5" customHeight="1">
@@ -24919,25 +24930,37 @@
         <v>1671</v>
       </c>
       <c r="B45" t="s">
-        <v>1995</v>
+        <v>862</v>
       </c>
       <c r="C45" t="s">
-        <v>1996</v>
+        <v>1992</v>
       </c>
       <c r="D45" t="s">
-        <v>1997</v>
+        <v>1993</v>
       </c>
       <c r="E45" t="s">
         <v>46</v>
       </c>
       <c r="F45" t="s">
+        <v>1994</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1995</v>
+      </c>
+      <c r="I45" t="s">
+        <v>1996</v>
+      </c>
+      <c r="J45" t="s">
+        <v>1709</v>
+      </c>
+      <c r="K45" t="s">
+        <v>1997</v>
+      </c>
+      <c r="L45" t="s">
         <v>1998</v>
       </c>
-      <c r="G45" t="s">
+      <c r="M45" t="s">
         <v>1999</v>
-      </c>
-      <c r="H45" t="s">
-        <v>2000</v>
       </c>
       <c r="N45" t="s">
         <v>52</v>
@@ -24946,22 +24969,22 @@
         <v>1681</v>
       </c>
       <c r="P45" t="s">
-        <v>2001</v>
+        <v>870</v>
       </c>
       <c r="Q45" t="s">
         <v>53</v>
       </c>
       <c r="R45" t="s">
-        <v>2002</v>
+        <v>2000</v>
       </c>
       <c r="S45" s="2">
-        <v>46142.64671296296</v>
+        <v>46154.834027777775</v>
       </c>
       <c r="T45" s="2">
-        <v>46133.616041666668</v>
+        <v>46154.814571759256</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>44</v>
       </c>
     </row>
     <row r="46" spans="1:21" ht="25.5" customHeight="1">
@@ -24969,28 +24992,25 @@
         <v>1671</v>
       </c>
       <c r="B46" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="C46" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D46" t="s">
         <v>2003</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
+        <v>46</v>
+      </c>
+      <c r="F46" t="s">
         <v>2004</v>
       </c>
-      <c r="E46" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" t="s">
+      <c r="G46" t="s">
         <v>2005</v>
       </c>
-      <c r="G46" t="s">
+      <c r="H46" t="s">
         <v>2006</v>
-      </c>
-      <c r="H46" t="s">
-        <v>2007</v>
-      </c>
-      <c r="I46" t="s">
-        <v>514</v>
       </c>
       <c r="N46" t="s">
         <v>52</v>
@@ -24999,22 +25019,22 @@
         <v>1681</v>
       </c>
       <c r="P46" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="Q46" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R46" t="s">
         <v>2008</v>
       </c>
       <c r="S46" s="2">
-        <v>46162.798391203702</v>
+        <v>46142.64671296296</v>
       </c>
       <c r="T46" s="2">
-        <v>46162.79792824074</v>
+        <v>46133.616041666668</v>
       </c>
       <c r="U46">
-        <v>60</v>
+        <v>1</v>
       </c>
     </row>
     <row r="47" spans="1:21" ht="25.5" customHeight="1">
@@ -25022,7 +25042,7 @@
         <v>1671</v>
       </c>
       <c r="B47" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="C47" t="s">
         <v>2009</v>
@@ -25031,7 +25051,7 @@
         <v>2010</v>
       </c>
       <c r="E47" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F47" t="s">
         <v>2011</v>
@@ -25042,6 +25062,9 @@
       <c r="H47" t="s">
         <v>2013</v>
       </c>
+      <c r="I47" t="s">
+        <v>514</v>
+      </c>
       <c r="N47" t="s">
         <v>52</v>
       </c>
@@ -25049,22 +25072,22 @@
         <v>1681</v>
       </c>
       <c r="P47" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="Q47" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R47" t="s">
         <v>2014</v>
       </c>
       <c r="S47" s="2">
-        <v>46189.843784722223</v>
+        <v>46162.798391203702</v>
       </c>
       <c r="T47" s="2">
-        <v>46189.842499999999</v>
+        <v>46162.79792824074</v>
       </c>
       <c r="U47">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="48" spans="1:21" ht="25.5" customHeight="1">
@@ -25072,7 +25095,7 @@
         <v>1671</v>
       </c>
       <c r="B48" t="s">
-        <v>1582</v>
+        <v>2001</v>
       </c>
       <c r="C48" t="s">
         <v>2015</v>
@@ -25092,15 +25115,6 @@
       <c r="H48" t="s">
         <v>2019</v>
       </c>
-      <c r="K48" t="s">
-        <v>2020</v>
-      </c>
-      <c r="L48" t="s">
-        <v>2021</v>
-      </c>
-      <c r="M48" t="s">
-        <v>2022</v>
-      </c>
       <c r="N48" t="s">
         <v>52</v>
       </c>
@@ -25108,22 +25122,22 @@
         <v>1681</v>
       </c>
       <c r="P48" t="s">
-        <v>1590</v>
+        <v>2007</v>
       </c>
       <c r="Q48" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="R48" t="s">
-        <v>2023</v>
+        <v>2020</v>
       </c>
       <c r="S48" s="2">
-        <v>46197.770914351851</v>
+        <v>46189.843784722223</v>
       </c>
       <c r="T48" s="2">
-        <v>46155.780578703707</v>
+        <v>46189.842499999999</v>
       </c>
       <c r="U48">
-        <v>48</v>
+        <v>62</v>
       </c>
     </row>
     <row r="49" spans="1:21" ht="25.5" customHeight="1">
@@ -25131,31 +25145,34 @@
         <v>1671</v>
       </c>
       <c r="B49" t="s">
+        <v>1582</v>
+      </c>
+      <c r="C49" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E49" t="s">
+        <v>46</v>
+      </c>
+      <c r="F49" t="s">
+        <v>2023</v>
+      </c>
+      <c r="G49" t="s">
         <v>2024</v>
       </c>
-      <c r="C49" t="s">
+      <c r="H49" t="s">
         <v>2025</v>
       </c>
-      <c r="D49" t="s">
+      <c r="K49" t="s">
         <v>2026</v>
       </c>
-      <c r="E49" t="s">
-        <v>25</v>
-      </c>
-      <c r="F49" t="s">
+      <c r="L49" t="s">
         <v>2027</v>
       </c>
-      <c r="G49" t="s">
+      <c r="M49" t="s">
         <v>2028</v>
-      </c>
-      <c r="H49" t="s">
-        <v>2029</v>
-      </c>
-      <c r="L49" t="s">
-        <v>2030</v>
-      </c>
-      <c r="M49" t="s">
-        <v>2031</v>
       </c>
       <c r="N49" t="s">
         <v>52</v>
@@ -25164,22 +25181,22 @@
         <v>1681</v>
       </c>
       <c r="P49" t="s">
-        <v>2032</v>
+        <v>1590</v>
       </c>
       <c r="Q49" t="s">
         <v>53</v>
       </c>
       <c r="R49" t="s">
-        <v>2033</v>
+        <v>2029</v>
       </c>
       <c r="S49" s="2">
-        <v>46223.738842592589</v>
+        <v>46197.770914351851</v>
       </c>
       <c r="T49" s="2">
-        <v>46189.852453703701</v>
+        <v>46155.780578703707</v>
       </c>
       <c r="U49">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="50" spans="1:21" ht="25.5" customHeight="1">
@@ -25187,37 +25204,31 @@
         <v>1671</v>
       </c>
       <c r="B50" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C50" t="s">
-        <v>2034</v>
+        <v>2031</v>
       </c>
       <c r="D50" t="s">
-        <v>2035</v>
+        <v>2032</v>
       </c>
       <c r="E50" t="s">
         <v>25</v>
       </c>
       <c r="F50" t="s">
+        <v>2033</v>
+      </c>
+      <c r="G50" t="s">
+        <v>2034</v>
+      </c>
+      <c r="H50" t="s">
+        <v>2035</v>
+      </c>
+      <c r="L50" t="s">
         <v>2036</v>
       </c>
-      <c r="G50" t="s">
+      <c r="M50" t="s">
         <v>2037</v>
-      </c>
-      <c r="H50" t="s">
-        <v>2038</v>
-      </c>
-      <c r="I50" t="s">
-        <v>2039</v>
-      </c>
-      <c r="J50" t="s">
-        <v>2040</v>
-      </c>
-      <c r="L50" t="s">
-        <v>2041</v>
-      </c>
-      <c r="M50" t="s">
-        <v>1680</v>
       </c>
       <c r="N50" t="s">
         <v>52</v>
@@ -25226,22 +25237,22 @@
         <v>1681</v>
       </c>
       <c r="P50" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="Q50" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R50" t="s">
-        <v>2042</v>
+        <v>2039</v>
       </c>
       <c r="S50" s="2">
-        <v>46262.777812499997</v>
+        <v>46223.738842592589</v>
       </c>
       <c r="T50" s="2">
-        <v>46197.767592592594</v>
+        <v>46189.852453703701</v>
       </c>
       <c r="U50">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="51" spans="1:21" ht="25.5" customHeight="1">
@@ -25249,31 +25260,37 @@
         <v>1671</v>
       </c>
       <c r="B51" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C51" t="s">
-        <v>2043</v>
+        <v>2040</v>
       </c>
       <c r="D51" t="s">
-        <v>2044</v>
+        <v>2041</v>
       </c>
       <c r="E51" t="s">
         <v>25</v>
       </c>
       <c r="F51" t="s">
+        <v>2042</v>
+      </c>
+      <c r="G51" t="s">
+        <v>2043</v>
+      </c>
+      <c r="H51" t="s">
+        <v>2044</v>
+      </c>
+      <c r="I51" t="s">
         <v>2045</v>
       </c>
-      <c r="G51" t="s">
+      <c r="J51" t="s">
         <v>2046</v>
       </c>
-      <c r="H51" t="s">
+      <c r="L51" t="s">
         <v>2047</v>
       </c>
-      <c r="I51" t="s">
-        <v>2048</v>
-      </c>
-      <c r="J51" t="s">
-        <v>2049</v>
+      <c r="M51" t="s">
+        <v>1680</v>
       </c>
       <c r="N51" t="s">
         <v>52</v>
@@ -25282,22 +25299,22 @@
         <v>1681</v>
       </c>
       <c r="P51" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="Q51" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R51" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="S51" s="2">
-        <v>46213.73605324074</v>
+        <v>46262.777812499997</v>
       </c>
       <c r="T51" s="2">
-        <v>46213.731365740743</v>
+        <v>46197.767592592594</v>
       </c>
       <c r="U51">
-        <v>72</v>
+        <v>65</v>
       </c>
     </row>
     <row r="52" spans="1:21" ht="25.5" customHeight="1">
@@ -25305,24 +25322,30 @@
         <v>1671</v>
       </c>
       <c r="B52" t="s">
-        <v>22</v>
+        <v>2030</v>
       </c>
       <c r="C52" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D52" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E52" t="s">
+        <v>25</v>
+      </c>
+      <c r="F52" t="s">
         <v>2051</v>
       </c>
-      <c r="D52" t="s">
+      <c r="G52" t="s">
         <v>2052</v>
       </c>
-      <c r="E52" t="s">
-        <v>46</v>
-      </c>
-      <c r="F52" t="s">
+      <c r="H52" t="s">
         <v>2053</v>
       </c>
-      <c r="G52" t="s">
+      <c r="I52" t="s">
         <v>2054</v>
       </c>
-      <c r="H52" t="s">
+      <c r="J52" t="s">
         <v>2055</v>
       </c>
       <c r="N52" t="s">
@@ -25332,22 +25355,22 @@
         <v>1681</v>
       </c>
       <c r="P52" t="s">
-        <v>32</v>
+        <v>2038</v>
       </c>
       <c r="Q52" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="R52" t="s">
         <v>2056</v>
       </c>
       <c r="S52" s="2">
-        <v>46161.645914351851</v>
+        <v>46213.73605324074</v>
       </c>
       <c r="T52" s="2">
-        <v>46161.645439814813</v>
+        <v>46213.731365740743</v>
       </c>
       <c r="U52">
-        <v>54</v>
+        <v>72</v>
       </c>
     </row>
     <row r="53" spans="1:21" ht="25.5" customHeight="1">
@@ -25385,7 +25408,7 @@
         <v>32</v>
       </c>
       <c r="Q53" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R53" t="s">
         <v>2062</v>
@@ -25394,10 +25417,10 @@
         <v>46161.645914351851</v>
       </c>
       <c r="T53" s="2">
-        <v>46161.645462962966</v>
+        <v>46161.645439814813</v>
       </c>
       <c r="U53">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="54" spans="1:21" ht="25.5" customHeight="1">
@@ -25435,7 +25458,7 @@
         <v>32</v>
       </c>
       <c r="Q54" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="R54" t="s">
         <v>2068</v>
@@ -25447,7 +25470,7 @@
         <v>46161.645462962966</v>
       </c>
       <c r="U54">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:21" ht="25.5" customHeight="1">
@@ -25455,7 +25478,7 @@
         <v>1671</v>
       </c>
       <c r="B55" t="s">
-        <v>1510</v>
+        <v>22</v>
       </c>
       <c r="C55" t="s">
         <v>2069</v>
@@ -25464,7 +25487,7 @@
         <v>2070</v>
       </c>
       <c r="E55" t="s">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="F55" t="s">
         <v>2071</v>
@@ -25482,22 +25505,22 @@
         <v>1681</v>
       </c>
       <c r="P55" t="s">
-        <v>1516</v>
+        <v>32</v>
       </c>
       <c r="Q55" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="R55" t="s">
         <v>2074</v>
       </c>
       <c r="S55" s="2">
-        <v>46161.759351851855</v>
+        <v>46161.645914351851</v>
       </c>
       <c r="T55" s="2">
-        <v>46161.756307870368</v>
+        <v>46161.645462962966</v>
       </c>
       <c r="U55">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="56" spans="1:21" ht="25.5" customHeight="1">
@@ -25514,7 +25537,7 @@
         <v>2076</v>
       </c>
       <c r="E56" t="s">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="F56" t="s">
         <v>2077</v>
@@ -25525,12 +25548,6 @@
       <c r="H56" t="s">
         <v>2079</v>
       </c>
-      <c r="L56" t="s">
-        <v>2080</v>
-      </c>
-      <c r="M56" t="s">
-        <v>2081</v>
-      </c>
       <c r="N56" t="s">
         <v>52</v>
       </c>
@@ -25541,19 +25558,19 @@
         <v>1516</v>
       </c>
       <c r="Q56" t="s">
-        <v>33</v>
+        <v>53</v>
       </c>
       <c r="R56" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="S56" s="2">
-        <v>46161.761087962965</v>
+        <v>46161.759351851855</v>
       </c>
       <c r="T56" s="2">
-        <v>46161.759664351855</v>
+        <v>46161.756307870368</v>
       </c>
       <c r="U56">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="57" spans="1:21" ht="25.5" customHeight="1">
@@ -25561,31 +25578,31 @@
         <v>1671</v>
       </c>
       <c r="B57" t="s">
+        <v>1510</v>
+      </c>
+      <c r="C57" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D57" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E57" t="s">
+        <v>46</v>
+      </c>
+      <c r="F57" t="s">
         <v>2083</v>
       </c>
-      <c r="C57" t="s">
+      <c r="G57" t="s">
         <v>2084</v>
       </c>
-      <c r="D57" t="s">
+      <c r="H57" t="s">
         <v>2085</v>
       </c>
-      <c r="E57" t="s">
-        <v>25</v>
-      </c>
-      <c r="F57" t="s">
+      <c r="L57" t="s">
         <v>2086</v>
       </c>
-      <c r="G57" t="s">
+      <c r="M57" t="s">
         <v>2087</v>
-      </c>
-      <c r="H57" t="s">
-        <v>2088</v>
-      </c>
-      <c r="L57" t="s">
-        <v>2041</v>
-      </c>
-      <c r="M57" t="s">
-        <v>1680</v>
       </c>
       <c r="N57" t="s">
         <v>52</v>
@@ -25594,22 +25611,22 @@
         <v>1681</v>
       </c>
       <c r="P57" t="s">
-        <v>2089</v>
+        <v>1516</v>
       </c>
       <c r="Q57" t="s">
-        <v>53</v>
+        <v>33</v>
       </c>
       <c r="R57" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="S57" s="2">
-        <v>46189.822222222225</v>
+        <v>46161.761087962965</v>
       </c>
       <c r="T57" s="2">
-        <v>46189.819675925923</v>
+        <v>46161.759664351855</v>
       </c>
       <c r="U57">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:21" ht="25.5" customHeight="1">
@@ -25617,28 +25634,31 @@
         <v>1671</v>
       </c>
       <c r="B58" t="s">
-        <v>1477</v>
+        <v>2089</v>
       </c>
       <c r="C58" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D58" t="s">
         <v>2091</v>
-      </c>
-      <c r="D58" t="s">
-        <v>2092</v>
       </c>
       <c r="E58" t="s">
         <v>25</v>
       </c>
       <c r="F58" t="s">
+        <v>2092</v>
+      </c>
+      <c r="G58" t="s">
         <v>2093</v>
       </c>
-      <c r="G58" t="s">
+      <c r="H58" t="s">
         <v>2094</v>
       </c>
-      <c r="I58" t="s">
-        <v>2095</v>
-      </c>
-      <c r="J58" t="s">
-        <v>1709</v>
+      <c r="L58" t="s">
+        <v>2047</v>
+      </c>
+      <c r="M58" t="s">
+        <v>1680</v>
       </c>
       <c r="N58" t="s">
         <v>52</v>
@@ -25647,7 +25667,7 @@
         <v>1681</v>
       </c>
       <c r="P58" t="s">
-        <v>1484</v>
+        <v>2095</v>
       </c>
       <c r="Q58" t="s">
         <v>53</v>
@@ -25656,13 +25676,13 @@
         <v>2096</v>
       </c>
       <c r="S58" s="2">
-        <v>46223.739166666666</v>
+        <v>46189.822222222225</v>
       </c>
       <c r="T58" s="2">
-        <v>46197.865810185183</v>
+        <v>46189.819675925923</v>
       </c>
       <c r="U58">
-        <v>66</v>
+        <v>61</v>
       </c>
     </row>
     <row r="59" spans="1:21" ht="25.5" customHeight="1">
@@ -25670,58 +25690,111 @@
         <v>1671</v>
       </c>
       <c r="B59" t="s">
-        <v>1278</v>
+        <v>1477</v>
       </c>
       <c r="C59" t="s">
-        <v>1407</v>
+        <v>2097</v>
       </c>
       <c r="D59" t="s">
-        <v>1408</v>
+        <v>2098</v>
       </c>
       <c r="E59" t="s">
         <v>25</v>
       </c>
       <c r="F59" t="s">
-        <v>1409</v>
+        <v>2099</v>
       </c>
       <c r="G59" t="s">
-        <v>1410</v>
-      </c>
-      <c r="H59" t="s">
-        <v>2097</v>
+        <v>2100</v>
+      </c>
+      <c r="I59" t="s">
+        <v>2101</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1709</v>
+      </c>
+      <c r="N59" t="s">
+        <v>52</v>
       </c>
       <c r="O59" t="s">
         <v>1681</v>
       </c>
       <c r="P59" t="s">
-        <v>1287</v>
+        <v>1484</v>
       </c>
       <c r="Q59" t="s">
         <v>53</v>
       </c>
       <c r="R59" t="s">
-        <v>2098</v>
+        <v>2102</v>
       </c>
       <c r="S59" s="2">
+        <v>46223.739166666666</v>
+      </c>
+      <c r="T59" s="2">
+        <v>46197.865810185183</v>
+      </c>
+      <c r="U59">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" ht="25.5" customHeight="1">
+      <c r="A60" t="s">
+        <v>1671</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1278</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1407</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1408</v>
+      </c>
+      <c r="E60" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1409</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1410</v>
+      </c>
+      <c r="H60" t="s">
+        <v>2103</v>
+      </c>
+      <c r="O60" t="s">
+        <v>1681</v>
+      </c>
+      <c r="P60" t="s">
+        <v>1287</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>53</v>
+      </c>
+      <c r="R60" t="s">
+        <v>2104</v>
+      </c>
+      <c r="S60" s="2">
         <v>46261.656284722223</v>
       </c>
-      <c r="T59" s="2">
+      <c r="T60" s="2">
         <v>46261.656111111108</v>
       </c>
-      <c r="U59">
+      <c r="U60">
         <v>74</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="B2:B58" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" sqref="B2:B59" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"代理问题,工具异常,环境列表与字段可见性,环境启动,网络问题,账号注册,访问控制,扩展安装,内核问题,订阅异常,下载问题,账号共享与安全,安装问题,窗口同步,访问问题,API咨询,RPA能力,系统异常,系统兼容,缓存设置,账号风控,成员管理"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E58" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" sqref="E2:E59" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"1,2,3,4"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N2:N58" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" sqref="N2:N59" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"all,client,end_user"</formula1>
     </dataValidation>
   </dataValidations>
@@ -25730,7 +25803,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FCDC47AE-6707-4ABC-A8FA-DCD0EEC679F7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C55D0133-D21E-4137-A1F9-D977426C5358}">
   <dimension ref="A1:T26"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -25739,10 +25812,10 @@
   <sheetData>
     <row r="1" spans="1:20" ht="12.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2099</v>
+        <v>2105</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2100</v>
+        <v>2106</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
@@ -25763,1461 +25836,1461 @@
         <v>2</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>2101</v>
+        <v>2107</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>2102</v>
+        <v>2108</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>2103</v>
+        <v>2109</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>2104</v>
+        <v>2110</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>2105</v>
+        <v>2111</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>2106</v>
+        <v>2112</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>2107</v>
+        <v>2113</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>2108</v>
+        <v>2114</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>2109</v>
+        <v>2115</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>2110</v>
+        <v>2116</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>2111</v>
+        <v>2117</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>2112</v>
+        <v>2118</v>
       </c>
     </row>
     <row r="2" spans="1:20" ht="25.5" customHeight="1">
       <c r="A2" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B2" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C2" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D2" t="s">
-        <v>2116</v>
+        <v>2122</v>
       </c>
       <c r="E2" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F2" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G2" t="s">
-        <v>2119</v>
+        <v>2125</v>
       </c>
       <c r="H2" t="s">
-        <v>2120</v>
+        <v>2126</v>
       </c>
       <c r="I2" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J2" t="s">
-        <v>2122</v>
+        <v>2128</v>
       </c>
       <c r="K2" t="s">
-        <v>2123</v>
+        <v>2129</v>
       </c>
       <c r="L2" t="s">
-        <v>2124</v>
+        <v>2130</v>
       </c>
       <c r="M2" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="O2" t="s">
-        <v>2126</v>
+        <v>2132</v>
       </c>
       <c r="P2" t="s">
-        <v>2127</v>
+        <v>2133</v>
       </c>
       <c r="Q2" t="s">
-        <v>2128</v>
+        <v>2134</v>
       </c>
       <c r="R2" t="s">
-        <v>2129</v>
+        <v>2135</v>
       </c>
       <c r="T2" t="s">
-        <v>2130</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="3" spans="1:20" ht="25.5" customHeight="1">
       <c r="A3" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B3" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C3" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D3" t="s">
-        <v>2116</v>
+        <v>2122</v>
       </c>
       <c r="E3" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F3" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G3" t="s">
-        <v>2119</v>
+        <v>2125</v>
       </c>
       <c r="H3" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I3" t="s">
+        <v>2127</v>
+      </c>
+      <c r="J3" t="s">
+        <v>2128</v>
+      </c>
+      <c r="K3" t="s">
+        <v>2129</v>
+      </c>
+      <c r="L3" t="s">
+        <v>2138</v>
+      </c>
+      <c r="M3" t="s">
         <v>2131</v>
       </c>
-      <c r="I3" t="s">
-        <v>2121</v>
-      </c>
-      <c r="J3" t="s">
-        <v>2122</v>
-      </c>
-      <c r="K3" t="s">
-        <v>2123</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="O3" t="s">
         <v>2132</v>
       </c>
-      <c r="M3" t="s">
-        <v>2125</v>
-      </c>
-      <c r="O3" t="s">
-        <v>2126</v>
-      </c>
       <c r="P3" t="s">
-        <v>2127</v>
+        <v>2133</v>
       </c>
       <c r="Q3" t="s">
-        <v>2133</v>
+        <v>2139</v>
       </c>
       <c r="R3" t="s">
-        <v>2134</v>
+        <v>2140</v>
       </c>
       <c r="T3" t="s">
-        <v>2135</v>
+        <v>2141</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="25.5" customHeight="1">
       <c r="A4" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B4" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C4" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D4" t="s">
-        <v>2116</v>
+        <v>2122</v>
       </c>
       <c r="E4" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F4" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G4" t="s">
-        <v>2119</v>
+        <v>2125</v>
       </c>
       <c r="H4" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I4" t="s">
+        <v>2127</v>
+      </c>
+      <c r="J4" t="s">
+        <v>2128</v>
+      </c>
+      <c r="K4" t="s">
+        <v>2129</v>
+      </c>
+      <c r="L4" t="s">
+        <v>2142</v>
+      </c>
+      <c r="M4" t="s">
         <v>2131</v>
       </c>
-      <c r="I4" t="s">
-        <v>2121</v>
-      </c>
-      <c r="J4" t="s">
-        <v>2122</v>
-      </c>
-      <c r="K4" t="s">
-        <v>2123</v>
-      </c>
-      <c r="L4" t="s">
-        <v>2136</v>
-      </c>
-      <c r="M4" t="s">
-        <v>2125</v>
-      </c>
       <c r="O4" t="s">
-        <v>2126</v>
+        <v>2132</v>
       </c>
       <c r="P4" t="s">
-        <v>2127</v>
+        <v>2133</v>
       </c>
       <c r="Q4" t="s">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="R4" t="s">
-        <v>2138</v>
+        <v>2144</v>
       </c>
       <c r="T4" t="s">
-        <v>2139</v>
+        <v>2145</v>
       </c>
     </row>
     <row r="5" spans="1:20" ht="25.5" customHeight="1">
       <c r="A5" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B5" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C5" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D5" t="s">
-        <v>2116</v>
+        <v>2122</v>
       </c>
       <c r="E5" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F5" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G5" t="s">
-        <v>2119</v>
+        <v>2125</v>
       </c>
       <c r="H5" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I5" t="s">
+        <v>2127</v>
+      </c>
+      <c r="J5" t="s">
+        <v>2142</v>
+      </c>
+      <c r="K5" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L5" t="s">
+        <v>2130</v>
+      </c>
+      <c r="M5" t="s">
         <v>2131</v>
       </c>
-      <c r="I5" t="s">
-        <v>2121</v>
-      </c>
-      <c r="J5" t="s">
-        <v>2136</v>
-      </c>
-      <c r="K5" t="s">
-        <v>2140</v>
-      </c>
-      <c r="L5" t="s">
-        <v>2124</v>
-      </c>
-      <c r="M5" t="s">
-        <v>2125</v>
-      </c>
       <c r="N5" t="s">
-        <v>2141</v>
+        <v>2147</v>
       </c>
       <c r="O5" t="s">
-        <v>2142</v>
+        <v>2148</v>
       </c>
       <c r="P5" t="s">
-        <v>2127</v>
+        <v>2133</v>
       </c>
       <c r="Q5" t="s">
-        <v>2128</v>
+        <v>2134</v>
       </c>
       <c r="R5" t="s">
-        <v>2143</v>
+        <v>2149</v>
       </c>
       <c r="T5" t="s">
-        <v>2144</v>
+        <v>2150</v>
       </c>
     </row>
     <row r="6" spans="1:20" ht="25.5" customHeight="1">
       <c r="A6" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B6" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C6" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D6" t="s">
-        <v>2116</v>
+        <v>2122</v>
       </c>
       <c r="E6" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F6" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G6" t="s">
-        <v>2119</v>
+        <v>2125</v>
       </c>
       <c r="H6" t="s">
+        <v>2137</v>
+      </c>
+      <c r="I6" t="s">
+        <v>2127</v>
+      </c>
+      <c r="J6" t="s">
+        <v>2142</v>
+      </c>
+      <c r="K6" t="s">
+        <v>2146</v>
+      </c>
+      <c r="L6" t="s">
+        <v>2151</v>
+      </c>
+      <c r="M6" t="s">
         <v>2131</v>
       </c>
-      <c r="I6" t="s">
-        <v>2121</v>
-      </c>
-      <c r="J6" t="s">
-        <v>2136</v>
-      </c>
-      <c r="K6" t="s">
-        <v>2140</v>
-      </c>
-      <c r="L6" t="s">
-        <v>2145</v>
-      </c>
-      <c r="M6" t="s">
-        <v>2125</v>
-      </c>
       <c r="N6" t="s">
-        <v>2141</v>
+        <v>2147</v>
       </c>
       <c r="O6" t="s">
-        <v>2142</v>
+        <v>2148</v>
       </c>
       <c r="P6" t="s">
-        <v>2127</v>
+        <v>2133</v>
       </c>
       <c r="Q6" t="s">
-        <v>2133</v>
+        <v>2139</v>
       </c>
       <c r="R6" t="s">
-        <v>2146</v>
+        <v>2152</v>
       </c>
       <c r="T6" t="s">
-        <v>2147</v>
+        <v>2153</v>
       </c>
     </row>
     <row r="7" spans="1:20" ht="25.5" customHeight="1">
       <c r="A7" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B7" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C7" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D7" t="s">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="E7" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F7" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G7" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="H7" t="s">
-        <v>2150</v>
+        <v>2156</v>
       </c>
       <c r="I7" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J7" t="s">
-        <v>2124</v>
+        <v>2130</v>
       </c>
       <c r="K7" t="s">
-        <v>2151</v>
+        <v>2157</v>
       </c>
       <c r="L7" t="s">
-        <v>2152</v>
+        <v>2158</v>
       </c>
       <c r="M7" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N7" t="s">
-        <v>2153</v>
+        <v>2159</v>
       </c>
       <c r="O7" t="s">
-        <v>2154</v>
+        <v>2160</v>
       </c>
       <c r="P7" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q7" t="s">
         <v>1695</v>
       </c>
       <c r="R7" t="s">
-        <v>2156</v>
+        <v>2162</v>
       </c>
       <c r="T7" t="s">
-        <v>2157</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="8" spans="1:20" ht="25.5" customHeight="1">
       <c r="A8" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B8" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C8" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D8" t="s">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="E8" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F8" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G8" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="H8" t="s">
-        <v>2150</v>
+        <v>2156</v>
       </c>
       <c r="I8" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J8" t="s">
-        <v>2124</v>
+        <v>2130</v>
       </c>
       <c r="K8" t="s">
-        <v>2151</v>
+        <v>2157</v>
       </c>
       <c r="L8" t="s">
-        <v>2158</v>
+        <v>2164</v>
       </c>
       <c r="M8" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N8" t="s">
-        <v>2153</v>
+        <v>2159</v>
       </c>
       <c r="O8" t="s">
-        <v>2154</v>
+        <v>2160</v>
       </c>
       <c r="P8" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q8" t="s">
-        <v>2159</v>
+        <v>2165</v>
       </c>
       <c r="R8" t="s">
-        <v>2160</v>
+        <v>2166</v>
       </c>
       <c r="T8" t="s">
-        <v>2161</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="9" spans="1:20" ht="25.5" customHeight="1">
       <c r="A9" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B9" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C9" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D9" t="s">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="E9" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F9" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G9" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="H9" t="s">
-        <v>2150</v>
+        <v>2156</v>
       </c>
       <c r="I9" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J9" t="s">
-        <v>2124</v>
+        <v>2130</v>
       </c>
       <c r="K9" t="s">
-        <v>2151</v>
+        <v>2157</v>
       </c>
       <c r="L9" t="s">
-        <v>2162</v>
+        <v>2168</v>
       </c>
       <c r="M9" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N9" t="s">
-        <v>2153</v>
+        <v>2159</v>
       </c>
       <c r="O9" t="s">
-        <v>2154</v>
+        <v>2160</v>
       </c>
       <c r="P9" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q9" t="s">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="R9" t="s">
-        <v>2163</v>
+        <v>2169</v>
       </c>
       <c r="T9" t="s">
-        <v>2164</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="10" spans="1:20" ht="25.5" customHeight="1">
       <c r="A10" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B10" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C10" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D10" t="s">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="E10" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F10" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G10" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="H10" t="s">
-        <v>2150</v>
+        <v>2156</v>
       </c>
       <c r="I10" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J10" t="s">
-        <v>2162</v>
+        <v>2168</v>
       </c>
       <c r="K10" t="s">
-        <v>2165</v>
+        <v>2171</v>
       </c>
       <c r="L10" t="s">
-        <v>2152</v>
+        <v>2158</v>
       </c>
       <c r="M10" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N10" t="s">
-        <v>2166</v>
+        <v>2172</v>
       </c>
       <c r="O10" t="s">
-        <v>2167</v>
+        <v>2173</v>
       </c>
       <c r="P10" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q10" t="s">
         <v>1695</v>
       </c>
       <c r="R10" t="s">
-        <v>2168</v>
+        <v>2174</v>
       </c>
       <c r="T10" t="s">
-        <v>2169</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="11" spans="1:20" ht="25.5" customHeight="1">
       <c r="A11" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B11" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C11" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D11" t="s">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="E11" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F11" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G11" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="H11" t="s">
-        <v>2150</v>
+        <v>2156</v>
       </c>
       <c r="I11" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J11" t="s">
-        <v>2162</v>
+        <v>2168</v>
       </c>
       <c r="K11" t="s">
+        <v>2171</v>
+      </c>
+      <c r="L11" t="s">
+        <v>2164</v>
+      </c>
+      <c r="M11" t="s">
+        <v>2131</v>
+      </c>
+      <c r="N11" t="s">
+        <v>2172</v>
+      </c>
+      <c r="O11" t="s">
+        <v>2173</v>
+      </c>
+      <c r="P11" t="s">
+        <v>2161</v>
+      </c>
+      <c r="Q11" t="s">
         <v>2165</v>
       </c>
-      <c r="L11" t="s">
-        <v>2158</v>
-      </c>
-      <c r="M11" t="s">
-        <v>2125</v>
-      </c>
-      <c r="N11" t="s">
-        <v>2166</v>
-      </c>
-      <c r="O11" t="s">
-        <v>2167</v>
-      </c>
-      <c r="P11" t="s">
-        <v>2155</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>2159</v>
-      </c>
       <c r="R11" t="s">
-        <v>2170</v>
+        <v>2176</v>
       </c>
       <c r="T11" t="s">
-        <v>2171</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="12" spans="1:20" ht="25.5" customHeight="1">
       <c r="A12" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B12" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C12" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D12" t="s">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="E12" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F12" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G12" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="H12" t="s">
-        <v>2150</v>
+        <v>2156</v>
       </c>
       <c r="I12" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J12" t="s">
-        <v>2152</v>
+        <v>2158</v>
       </c>
       <c r="K12" t="s">
-        <v>2172</v>
+        <v>2178</v>
       </c>
       <c r="L12" t="s">
-        <v>2173</v>
+        <v>2179</v>
       </c>
       <c r="M12" t="s">
-        <v>2174</v>
+        <v>2180</v>
       </c>
       <c r="N12" t="s">
-        <v>2175</v>
+        <v>2181</v>
       </c>
       <c r="S12" t="s">
-        <v>2176</v>
+        <v>2182</v>
       </c>
       <c r="T12" t="s">
-        <v>2177</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="13" spans="1:20" ht="25.5" customHeight="1">
       <c r="A13" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B13" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C13" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D13" t="s">
-        <v>2148</v>
+        <v>2154</v>
       </c>
       <c r="E13" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F13" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G13" t="s">
-        <v>2149</v>
+        <v>2155</v>
       </c>
       <c r="H13" t="s">
-        <v>2150</v>
+        <v>2156</v>
       </c>
       <c r="I13" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J13" t="s">
-        <v>2158</v>
+        <v>2164</v>
       </c>
       <c r="K13" t="s">
-        <v>2178</v>
+        <v>2184</v>
       </c>
       <c r="L13" t="s">
-        <v>2173</v>
+        <v>2179</v>
       </c>
       <c r="M13" t="s">
-        <v>2174</v>
+        <v>2180</v>
       </c>
       <c r="N13" t="s">
-        <v>2179</v>
+        <v>2185</v>
       </c>
       <c r="S13" t="s">
-        <v>2180</v>
+        <v>2186</v>
       </c>
       <c r="T13" t="s">
-        <v>2181</v>
+        <v>2187</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="25.5" customHeight="1">
       <c r="A14" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B14" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C14" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D14" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E14" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F14" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G14" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H14" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I14" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J14" t="s">
-        <v>2145</v>
+        <v>2151</v>
       </c>
       <c r="K14" t="s">
-        <v>2185</v>
+        <v>2191</v>
       </c>
       <c r="L14" t="s">
-        <v>2186</v>
+        <v>2192</v>
       </c>
       <c r="M14" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N14" t="s">
-        <v>2187</v>
+        <v>2193</v>
       </c>
       <c r="O14" t="s">
-        <v>2188</v>
+        <v>2194</v>
       </c>
       <c r="P14" t="s">
-        <v>2189</v>
+        <v>2195</v>
       </c>
       <c r="Q14" t="s">
-        <v>2190</v>
+        <v>2196</v>
       </c>
       <c r="R14" t="s">
-        <v>2191</v>
+        <v>2197</v>
       </c>
       <c r="T14" t="s">
-        <v>2192</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="15" spans="1:20" ht="25.5" customHeight="1">
       <c r="A15" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B15" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C15" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D15" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E15" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F15" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G15" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H15" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I15" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J15" t="s">
-        <v>2145</v>
+        <v>2151</v>
       </c>
       <c r="K15" t="s">
-        <v>2185</v>
+        <v>2191</v>
       </c>
       <c r="L15" t="s">
+        <v>2199</v>
+      </c>
+      <c r="M15" t="s">
+        <v>2131</v>
+      </c>
+      <c r="N15" t="s">
         <v>2193</v>
       </c>
-      <c r="M15" t="s">
-        <v>2125</v>
-      </c>
-      <c r="N15" t="s">
-        <v>2187</v>
-      </c>
       <c r="O15" t="s">
-        <v>2188</v>
+        <v>2194</v>
       </c>
       <c r="P15" t="s">
-        <v>2189</v>
+        <v>2195</v>
       </c>
       <c r="Q15" t="s">
-        <v>2194</v>
+        <v>2200</v>
       </c>
       <c r="R15" t="s">
-        <v>2195</v>
+        <v>2201</v>
       </c>
       <c r="T15" t="s">
-        <v>2196</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="16" spans="1:20" ht="25.5" customHeight="1">
       <c r="A16" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B16" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C16" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D16" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E16" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F16" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G16" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H16" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I16" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J16" t="s">
-        <v>2145</v>
+        <v>2151</v>
       </c>
       <c r="K16" t="s">
-        <v>2185</v>
+        <v>2191</v>
       </c>
       <c r="L16" t="s">
-        <v>2197</v>
+        <v>2203</v>
       </c>
       <c r="M16" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N16" t="s">
-        <v>2187</v>
+        <v>2193</v>
       </c>
       <c r="O16" t="s">
-        <v>2188</v>
+        <v>2194</v>
       </c>
       <c r="P16" t="s">
-        <v>2189</v>
+        <v>2195</v>
       </c>
       <c r="Q16" t="s">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="R16" t="s">
-        <v>2198</v>
+        <v>2204</v>
       </c>
       <c r="T16" t="s">
-        <v>2199</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="17" spans="1:20" ht="25.5" customHeight="1">
       <c r="A17" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B17" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C17" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D17" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E17" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F17" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G17" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H17" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I17" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J17" t="s">
-        <v>2197</v>
+        <v>2203</v>
       </c>
       <c r="K17" t="s">
-        <v>2200</v>
+        <v>2206</v>
       </c>
       <c r="L17" t="s">
-        <v>2186</v>
+        <v>2192</v>
       </c>
       <c r="M17" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N17" t="s">
-        <v>2201</v>
+        <v>2207</v>
       </c>
       <c r="O17" t="s">
-        <v>2202</v>
+        <v>2208</v>
       </c>
       <c r="P17" t="s">
-        <v>2189</v>
+        <v>2195</v>
       </c>
       <c r="Q17" t="s">
-        <v>2190</v>
+        <v>2196</v>
       </c>
       <c r="R17" t="s">
-        <v>2203</v>
+        <v>2209</v>
       </c>
       <c r="T17" t="s">
-        <v>2204</v>
+        <v>2210</v>
       </c>
     </row>
     <row r="18" spans="1:20" ht="25.5" customHeight="1">
       <c r="A18" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B18" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C18" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D18" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E18" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F18" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G18" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H18" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I18" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J18" t="s">
-        <v>2197</v>
+        <v>2203</v>
       </c>
       <c r="K18" t="s">
+        <v>2206</v>
+      </c>
+      <c r="L18" t="s">
+        <v>2199</v>
+      </c>
+      <c r="M18" t="s">
+        <v>2131</v>
+      </c>
+      <c r="N18" t="s">
+        <v>2207</v>
+      </c>
+      <c r="O18" t="s">
+        <v>2208</v>
+      </c>
+      <c r="P18" t="s">
+        <v>2195</v>
+      </c>
+      <c r="Q18" t="s">
         <v>2200</v>
       </c>
-      <c r="L18" t="s">
-        <v>2193</v>
-      </c>
-      <c r="M18" t="s">
-        <v>2125</v>
-      </c>
-      <c r="N18" t="s">
-        <v>2201</v>
-      </c>
-      <c r="O18" t="s">
-        <v>2202</v>
-      </c>
-      <c r="P18" t="s">
-        <v>2189</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>2194</v>
-      </c>
       <c r="R18" t="s">
-        <v>2205</v>
+        <v>2211</v>
       </c>
       <c r="T18" t="s">
-        <v>2206</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="19" spans="1:20" ht="25.5" customHeight="1">
       <c r="A19" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B19" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C19" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D19" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E19" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F19" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G19" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H19" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I19" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J19" t="s">
-        <v>2186</v>
+        <v>2192</v>
       </c>
       <c r="K19" t="s">
-        <v>2207</v>
+        <v>2213</v>
       </c>
       <c r="L19" t="s">
-        <v>2208</v>
+        <v>2214</v>
       </c>
       <c r="M19" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N19" t="s">
-        <v>2209</v>
+        <v>2215</v>
       </c>
       <c r="O19" t="s">
-        <v>2210</v>
+        <v>2216</v>
       </c>
       <c r="P19" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q19" t="s">
         <v>1695</v>
       </c>
       <c r="R19" t="s">
-        <v>2211</v>
+        <v>2217</v>
       </c>
       <c r="T19" t="s">
-        <v>2212</v>
+        <v>2218</v>
       </c>
     </row>
     <row r="20" spans="1:20" ht="25.5" customHeight="1">
       <c r="A20" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B20" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C20" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D20" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E20" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F20" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G20" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H20" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I20" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J20" t="s">
-        <v>2186</v>
+        <v>2192</v>
       </c>
       <c r="K20" t="s">
-        <v>2207</v>
+        <v>2213</v>
       </c>
       <c r="L20" t="s">
-        <v>2213</v>
+        <v>2219</v>
       </c>
       <c r="M20" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N20" t="s">
-        <v>2209</v>
+        <v>2215</v>
       </c>
       <c r="O20" t="s">
-        <v>2210</v>
+        <v>2216</v>
       </c>
       <c r="P20" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q20" t="s">
-        <v>2159</v>
+        <v>2165</v>
       </c>
       <c r="R20" t="s">
-        <v>2214</v>
+        <v>2220</v>
       </c>
       <c r="T20" t="s">
-        <v>2215</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="21" spans="1:20" ht="25.5" customHeight="1">
       <c r="A21" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B21" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C21" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D21" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E21" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F21" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G21" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H21" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I21" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J21" t="s">
-        <v>2186</v>
+        <v>2192</v>
       </c>
       <c r="K21" t="s">
-        <v>2207</v>
+        <v>2213</v>
       </c>
       <c r="L21" t="s">
+        <v>2222</v>
+      </c>
+      <c r="M21" t="s">
+        <v>2131</v>
+      </c>
+      <c r="N21" t="s">
+        <v>2215</v>
+      </c>
+      <c r="O21" t="s">
         <v>2216</v>
       </c>
-      <c r="M21" t="s">
-        <v>2125</v>
-      </c>
-      <c r="N21" t="s">
-        <v>2209</v>
-      </c>
-      <c r="O21" t="s">
-        <v>2210</v>
-      </c>
       <c r="P21" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q21" t="s">
-        <v>2137</v>
+        <v>2143</v>
       </c>
       <c r="R21" t="s">
-        <v>2217</v>
+        <v>2223</v>
       </c>
       <c r="T21" t="s">
-        <v>2218</v>
+        <v>2224</v>
       </c>
     </row>
     <row r="22" spans="1:20" ht="25.5" customHeight="1">
       <c r="A22" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B22" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C22" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D22" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E22" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F22" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G22" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H22" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I22" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J22" t="s">
-        <v>2216</v>
+        <v>2222</v>
       </c>
       <c r="K22" t="s">
-        <v>2219</v>
+        <v>2225</v>
       </c>
       <c r="L22" t="s">
-        <v>2208</v>
+        <v>2214</v>
       </c>
       <c r="M22" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N22" t="s">
-        <v>2220</v>
+        <v>2226</v>
       </c>
       <c r="O22" t="s">
-        <v>2221</v>
+        <v>2227</v>
       </c>
       <c r="P22" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q22" t="s">
         <v>1695</v>
       </c>
       <c r="R22" t="s">
-        <v>2222</v>
+        <v>2228</v>
       </c>
       <c r="T22" t="s">
-        <v>2223</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="23" spans="1:20" ht="25.5" customHeight="1">
       <c r="A23" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B23" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C23" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D23" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E23" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F23" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G23" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H23" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I23" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J23" t="s">
-        <v>2216</v>
+        <v>2222</v>
       </c>
       <c r="K23" t="s">
+        <v>2225</v>
+      </c>
+      <c r="L23" t="s">
         <v>2219</v>
       </c>
-      <c r="L23" t="s">
-        <v>2213</v>
-      </c>
       <c r="M23" t="s">
-        <v>2125</v>
+        <v>2131</v>
       </c>
       <c r="N23" t="s">
-        <v>2220</v>
+        <v>2226</v>
       </c>
       <c r="O23" t="s">
-        <v>2221</v>
+        <v>2227</v>
       </c>
       <c r="P23" t="s">
-        <v>2155</v>
+        <v>2161</v>
       </c>
       <c r="Q23" t="s">
-        <v>2159</v>
+        <v>2165</v>
       </c>
       <c r="R23" t="s">
-        <v>2224</v>
+        <v>2230</v>
       </c>
       <c r="T23" t="s">
-        <v>2225</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="24" spans="1:20" ht="25.5" customHeight="1">
       <c r="A24" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B24" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C24" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D24" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E24" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F24" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G24" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H24" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I24" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J24" t="s">
-        <v>2208</v>
+        <v>2214</v>
       </c>
       <c r="K24" t="s">
-        <v>2226</v>
+        <v>2232</v>
       </c>
       <c r="L24" t="s">
-        <v>2173</v>
+        <v>2179</v>
       </c>
       <c r="M24" t="s">
-        <v>2174</v>
+        <v>2180</v>
       </c>
       <c r="N24" t="s">
-        <v>2227</v>
+        <v>2233</v>
       </c>
       <c r="S24" t="s">
-        <v>2228</v>
+        <v>2234</v>
       </c>
       <c r="T24" t="s">
-        <v>2229</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="25" spans="1:20" ht="25.5" customHeight="1">
       <c r="A25" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B25" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C25" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D25" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E25" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F25" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G25" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H25" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I25" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J25" t="s">
-        <v>2213</v>
+        <v>2219</v>
       </c>
       <c r="K25" t="s">
-        <v>2230</v>
+        <v>2236</v>
       </c>
       <c r="L25" t="s">
-        <v>2173</v>
+        <v>2179</v>
       </c>
       <c r="M25" t="s">
-        <v>2174</v>
+        <v>2180</v>
       </c>
       <c r="N25" t="s">
-        <v>2231</v>
+        <v>2237</v>
       </c>
       <c r="S25" t="s">
-        <v>2232</v>
+        <v>2238</v>
       </c>
       <c r="T25" t="s">
-        <v>2233</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="26" spans="1:20" ht="25.5" customHeight="1">
       <c r="A26" t="s">
-        <v>2113</v>
+        <v>2119</v>
       </c>
       <c r="B26" t="s">
-        <v>2114</v>
+        <v>2120</v>
       </c>
       <c r="C26" t="s">
-        <v>2115</v>
+        <v>2121</v>
       </c>
       <c r="D26" t="s">
-        <v>2182</v>
+        <v>2188</v>
       </c>
       <c r="E26" t="s">
-        <v>2117</v>
+        <v>2123</v>
       </c>
       <c r="F26" t="s">
-        <v>2118</v>
+        <v>2124</v>
       </c>
       <c r="G26" t="s">
-        <v>2183</v>
+        <v>2189</v>
       </c>
       <c r="H26" t="s">
-        <v>2184</v>
+        <v>2190</v>
       </c>
       <c r="I26" t="s">
-        <v>2121</v>
+        <v>2127</v>
       </c>
       <c r="J26" t="s">
-        <v>2193</v>
+        <v>2199</v>
       </c>
       <c r="K26" t="s">
-        <v>2234</v>
+        <v>2240</v>
       </c>
       <c r="L26" t="s">
-        <v>2173</v>
+        <v>2179</v>
       </c>
       <c r="M26" t="s">
-        <v>2174</v>
+        <v>2180</v>
       </c>
       <c r="N26" t="s">
-        <v>2235</v>
+        <v>2241</v>
       </c>
       <c r="S26" t="s">
-        <v>2236</v>
+        <v>2242</v>
       </c>
       <c r="T26" t="s">
-        <v>2237</v>
+        <v>2243</v>
       </c>
     </row>
   </sheetData>
@@ -27227,7 +27300,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC0C7B75-42A0-4D40-AA7F-09E492068CB2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BAA0339-15BE-498F-A089-FD2775DFF0CD}">
   <dimension ref="A1:P50"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -27260,7 +27333,7 @@
         <v>7</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2238</v>
+        <v>2244</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>4</v>
@@ -27289,31 +27362,31 @@
     </row>
     <row r="2" spans="1:16" ht="25.5" customHeight="1">
       <c r="A2" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B2" t="s">
         <v>568</v>
       </c>
       <c r="C2" t="s">
-        <v>2240</v>
+        <v>2246</v>
       </c>
       <c r="D2" t="s">
-        <v>2241</v>
+        <v>2247</v>
       </c>
       <c r="E2" t="s">
-        <v>2242</v>
+        <v>2248</v>
       </c>
       <c r="F2" t="s">
-        <v>2243</v>
+        <v>2249</v>
       </c>
       <c r="G2" t="s">
         <v>1709</v>
       </c>
       <c r="J2" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K2" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L2" t="s">
         <v>574</v>
@@ -27322,7 +27395,7 @@
         <v>53</v>
       </c>
       <c r="N2" t="s">
-        <v>2246</v>
+        <v>2252</v>
       </c>
       <c r="O2" s="2">
         <v>46191.567939814813</v>
@@ -27333,31 +27406,31 @@
     </row>
     <row r="3" spans="1:16" ht="25.5" customHeight="1">
       <c r="A3" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B3" t="s">
         <v>568</v>
       </c>
       <c r="C3" t="s">
-        <v>2247</v>
+        <v>2253</v>
       </c>
       <c r="D3" t="s">
-        <v>2248</v>
+        <v>2254</v>
       </c>
       <c r="E3" t="s">
-        <v>2249</v>
+        <v>2255</v>
       </c>
       <c r="F3" t="s">
-        <v>2250</v>
+        <v>2256</v>
       </c>
       <c r="G3" t="s">
         <v>1709</v>
       </c>
       <c r="J3" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K3" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L3" t="s">
         <v>574</v>
@@ -27366,7 +27439,7 @@
         <v>33</v>
       </c>
       <c r="N3" t="s">
-        <v>2251</v>
+        <v>2257</v>
       </c>
       <c r="O3" s="2">
         <v>46133.665960648148</v>
@@ -27377,31 +27450,31 @@
     </row>
     <row r="4" spans="1:16" ht="25.5" customHeight="1">
       <c r="A4" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B4" t="s">
         <v>568</v>
       </c>
       <c r="C4" t="s">
-        <v>2252</v>
+        <v>2258</v>
       </c>
       <c r="D4" t="s">
-        <v>2253</v>
+        <v>2259</v>
       </c>
       <c r="E4" t="s">
-        <v>2254</v>
+        <v>2260</v>
       </c>
       <c r="F4" t="s">
-        <v>2255</v>
+        <v>2261</v>
       </c>
       <c r="G4" t="s">
         <v>1709</v>
       </c>
       <c r="J4" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K4" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L4" t="s">
         <v>574</v>
@@ -27410,7 +27483,7 @@
         <v>42</v>
       </c>
       <c r="N4" t="s">
-        <v>2256</v>
+        <v>2262</v>
       </c>
       <c r="O4" s="2">
         <v>46133.665960648148</v>
@@ -27421,31 +27494,31 @@
     </row>
     <row r="5" spans="1:16" ht="25.5" customHeight="1">
       <c r="A5" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B5" t="s">
         <v>568</v>
       </c>
       <c r="C5" t="s">
-        <v>2257</v>
+        <v>2263</v>
       </c>
       <c r="D5" t="s">
-        <v>2258</v>
+        <v>2264</v>
       </c>
       <c r="E5" t="s">
-        <v>2259</v>
+        <v>2265</v>
       </c>
       <c r="F5" t="s">
-        <v>2260</v>
+        <v>2266</v>
       </c>
       <c r="G5" t="s">
         <v>1709</v>
       </c>
       <c r="J5" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K5" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L5" t="s">
         <v>574</v>
@@ -27454,7 +27527,7 @@
         <v>62</v>
       </c>
       <c r="N5" t="s">
-        <v>2261</v>
+        <v>2267</v>
       </c>
       <c r="O5" s="2">
         <v>46197.866736111115</v>
@@ -27465,31 +27538,31 @@
     </row>
     <row r="6" spans="1:16" ht="25.5" customHeight="1">
       <c r="A6" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B6" t="s">
         <v>568</v>
       </c>
       <c r="C6" t="s">
-        <v>2262</v>
+        <v>2268</v>
       </c>
       <c r="D6" t="s">
-        <v>2263</v>
+        <v>2269</v>
       </c>
       <c r="E6" t="s">
-        <v>2264</v>
+        <v>2270</v>
       </c>
       <c r="F6" t="s">
-        <v>2265</v>
+        <v>2271</v>
       </c>
       <c r="G6" t="s">
         <v>1709</v>
       </c>
       <c r="J6" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K6" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L6" t="s">
         <v>574</v>
@@ -27498,7 +27571,7 @@
         <v>69</v>
       </c>
       <c r="N6" t="s">
-        <v>2266</v>
+        <v>2272</v>
       </c>
       <c r="O6" s="2">
         <v>46133.665960648148</v>
@@ -27509,31 +27582,31 @@
     </row>
     <row r="7" spans="1:16" ht="25.5" customHeight="1">
       <c r="A7" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B7" t="s">
         <v>568</v>
       </c>
       <c r="C7" t="s">
-        <v>2267</v>
+        <v>2273</v>
       </c>
       <c r="D7" t="s">
-        <v>2268</v>
+        <v>2274</v>
       </c>
       <c r="E7" t="s">
         <v>503</v>
       </c>
       <c r="F7" t="s">
-        <v>2269</v>
+        <v>2275</v>
       </c>
       <c r="G7" t="s">
         <v>1709</v>
       </c>
       <c r="J7" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K7" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L7" t="s">
         <v>574</v>
@@ -27542,7 +27615,7 @@
         <v>78</v>
       </c>
       <c r="N7" t="s">
-        <v>2270</v>
+        <v>2276</v>
       </c>
       <c r="O7" s="2">
         <v>46133.665960648148</v>
@@ -27553,31 +27626,31 @@
     </row>
     <row r="8" spans="1:16" ht="25.5" customHeight="1">
       <c r="A8" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B8" t="s">
         <v>568</v>
       </c>
       <c r="C8" t="s">
-        <v>2271</v>
+        <v>2277</v>
       </c>
       <c r="D8" t="s">
-        <v>2272</v>
+        <v>2278</v>
       </c>
       <c r="E8" t="s">
-        <v>2273</v>
+        <v>2279</v>
       </c>
       <c r="F8" t="s">
-        <v>2274</v>
+        <v>2280</v>
       </c>
       <c r="G8" t="s">
         <v>1709</v>
       </c>
       <c r="J8" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K8" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L8" t="s">
         <v>574</v>
@@ -27586,7 +27659,7 @@
         <v>85</v>
       </c>
       <c r="N8" t="s">
-        <v>2275</v>
+        <v>2281</v>
       </c>
       <c r="O8" s="2">
         <v>46133.665960648148</v>
@@ -27597,31 +27670,31 @@
     </row>
     <row r="9" spans="1:16" ht="25.5" customHeight="1">
       <c r="A9" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B9" t="s">
         <v>568</v>
       </c>
       <c r="C9" t="s">
-        <v>2276</v>
+        <v>2282</v>
       </c>
       <c r="D9" t="s">
-        <v>2277</v>
+        <v>2283</v>
       </c>
       <c r="E9" t="s">
-        <v>2278</v>
+        <v>2284</v>
       </c>
       <c r="F9" t="s">
-        <v>2279</v>
+        <v>2285</v>
       </c>
       <c r="G9" t="s">
         <v>1709</v>
       </c>
       <c r="J9" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K9" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L9" t="s">
         <v>574</v>
@@ -27630,7 +27703,7 @@
         <v>92</v>
       </c>
       <c r="N9" t="s">
-        <v>2280</v>
+        <v>2286</v>
       </c>
       <c r="O9" s="2">
         <v>46133.665960648148</v>
@@ -27641,31 +27714,31 @@
     </row>
     <row r="10" spans="1:16" ht="25.5" customHeight="1">
       <c r="A10" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B10" t="s">
         <v>568</v>
       </c>
       <c r="C10" t="s">
-        <v>2281</v>
+        <v>2287</v>
       </c>
       <c r="D10" t="s">
-        <v>2282</v>
+        <v>2288</v>
       </c>
       <c r="E10" t="s">
-        <v>2283</v>
+        <v>2289</v>
       </c>
       <c r="F10" t="s">
-        <v>2284</v>
+        <v>2290</v>
       </c>
       <c r="G10" t="s">
         <v>1709</v>
       </c>
       <c r="J10" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K10" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L10" t="s">
         <v>574</v>
@@ -27674,7 +27747,7 @@
         <v>99</v>
       </c>
       <c r="N10" t="s">
-        <v>2285</v>
+        <v>2291</v>
       </c>
       <c r="O10" s="2">
         <v>46133.665960648148</v>
@@ -27685,31 +27758,31 @@
     </row>
     <row r="11" spans="1:16" ht="25.5" customHeight="1">
       <c r="A11" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B11" t="s">
         <v>568</v>
       </c>
       <c r="C11" t="s">
-        <v>2286</v>
+        <v>2292</v>
       </c>
       <c r="D11" t="s">
-        <v>2287</v>
+        <v>2293</v>
       </c>
       <c r="E11" t="s">
-        <v>2288</v>
+        <v>2294</v>
       </c>
       <c r="F11" t="s">
-        <v>2289</v>
+        <v>2295</v>
       </c>
       <c r="G11" t="s">
         <v>1709</v>
       </c>
       <c r="J11" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K11" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L11" t="s">
         <v>574</v>
@@ -27718,7 +27791,7 @@
         <v>106</v>
       </c>
       <c r="N11" t="s">
-        <v>2290</v>
+        <v>2296</v>
       </c>
       <c r="O11" s="2">
         <v>46133.665960648148</v>
@@ -27729,31 +27802,31 @@
     </row>
     <row r="12" spans="1:16" ht="25.5" customHeight="1">
       <c r="A12" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B12" t="s">
         <v>568</v>
       </c>
       <c r="C12" t="s">
-        <v>2291</v>
+        <v>2297</v>
       </c>
       <c r="D12" t="s">
-        <v>2292</v>
+        <v>2298</v>
       </c>
       <c r="E12" t="s">
-        <v>2293</v>
+        <v>2299</v>
       </c>
       <c r="F12" t="s">
-        <v>2294</v>
+        <v>2300</v>
       </c>
       <c r="G12" t="s">
         <v>1709</v>
       </c>
       <c r="J12" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K12" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L12" t="s">
         <v>574</v>
@@ -27762,7 +27835,7 @@
         <v>113</v>
       </c>
       <c r="N12" t="s">
-        <v>2295</v>
+        <v>2301</v>
       </c>
       <c r="O12" s="2">
         <v>46133.665960648148</v>
@@ -27773,31 +27846,31 @@
     </row>
     <row r="13" spans="1:16" ht="25.5" customHeight="1">
       <c r="A13" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B13" t="s">
         <v>568</v>
       </c>
       <c r="C13" t="s">
-        <v>2296</v>
+        <v>2302</v>
       </c>
       <c r="D13" t="s">
-        <v>2297</v>
+        <v>2303</v>
       </c>
       <c r="E13" t="s">
-        <v>2298</v>
+        <v>2304</v>
       </c>
       <c r="F13" t="s">
-        <v>2299</v>
+        <v>2305</v>
       </c>
       <c r="G13" t="s">
         <v>1709</v>
       </c>
       <c r="J13" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K13" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L13" t="s">
         <v>574</v>
@@ -27806,7 +27879,7 @@
         <v>120</v>
       </c>
       <c r="N13" t="s">
-        <v>2300</v>
+        <v>2306</v>
       </c>
       <c r="O13" s="2">
         <v>46133.665960648148</v>
@@ -27817,31 +27890,31 @@
     </row>
     <row r="14" spans="1:16" ht="25.5" customHeight="1">
       <c r="A14" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B14" t="s">
         <v>568</v>
       </c>
       <c r="C14" t="s">
-        <v>2301</v>
+        <v>2307</v>
       </c>
       <c r="D14" t="s">
-        <v>2302</v>
+        <v>2308</v>
       </c>
       <c r="E14" t="s">
-        <v>2303</v>
+        <v>2309</v>
       </c>
       <c r="F14" t="s">
-        <v>2304</v>
+        <v>2310</v>
       </c>
       <c r="G14" t="s">
         <v>1709</v>
       </c>
       <c r="J14" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K14" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L14" t="s">
         <v>574</v>
@@ -27850,7 +27923,7 @@
         <v>127</v>
       </c>
       <c r="N14" t="s">
-        <v>2305</v>
+        <v>2311</v>
       </c>
       <c r="O14" s="2">
         <v>46133.665960648148</v>
@@ -27861,31 +27934,31 @@
     </row>
     <row r="15" spans="1:16" ht="25.5" customHeight="1">
       <c r="A15" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B15" t="s">
         <v>568</v>
       </c>
       <c r="C15" t="s">
-        <v>2306</v>
+        <v>2312</v>
       </c>
       <c r="D15" t="s">
-        <v>2307</v>
+        <v>2313</v>
       </c>
       <c r="E15" t="s">
-        <v>2308</v>
+        <v>2314</v>
       </c>
       <c r="F15" t="s">
-        <v>2309</v>
+        <v>2315</v>
       </c>
       <c r="G15" t="s">
         <v>1709</v>
       </c>
       <c r="J15" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K15" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L15" t="s">
         <v>574</v>
@@ -27894,7 +27967,7 @@
         <v>135</v>
       </c>
       <c r="N15" t="s">
-        <v>2310</v>
+        <v>2316</v>
       </c>
       <c r="O15" s="2">
         <v>46133.665960648148</v>
@@ -27905,31 +27978,31 @@
     </row>
     <row r="16" spans="1:16" ht="25.5" customHeight="1">
       <c r="A16" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B16" t="s">
         <v>568</v>
       </c>
       <c r="C16" t="s">
-        <v>2311</v>
+        <v>2317</v>
       </c>
       <c r="D16" t="s">
-        <v>2312</v>
+        <v>2318</v>
       </c>
       <c r="E16" t="s">
-        <v>2313</v>
+        <v>2319</v>
       </c>
       <c r="F16" t="s">
-        <v>2314</v>
+        <v>2320</v>
       </c>
       <c r="G16" t="s">
         <v>1709</v>
       </c>
       <c r="J16" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K16" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L16" t="s">
         <v>574</v>
@@ -27938,7 +28011,7 @@
         <v>142</v>
       </c>
       <c r="N16" t="s">
-        <v>2315</v>
+        <v>2321</v>
       </c>
       <c r="O16" s="2">
         <v>46133.665960648148</v>
@@ -27949,31 +28022,31 @@
     </row>
     <row r="17" spans="1:16" ht="25.5" customHeight="1">
       <c r="A17" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B17" t="s">
         <v>568</v>
       </c>
       <c r="C17" t="s">
-        <v>2316</v>
+        <v>2322</v>
       </c>
       <c r="D17" t="s">
-        <v>2317</v>
+        <v>2323</v>
       </c>
       <c r="E17" t="s">
-        <v>2318</v>
+        <v>2324</v>
       </c>
       <c r="F17" t="s">
-        <v>2319</v>
+        <v>2325</v>
       </c>
       <c r="G17" t="s">
         <v>1709</v>
       </c>
       <c r="J17" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K17" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L17" t="s">
         <v>574</v>
@@ -27982,7 +28055,7 @@
         <v>149</v>
       </c>
       <c r="N17" t="s">
-        <v>2320</v>
+        <v>2326</v>
       </c>
       <c r="O17" s="2">
         <v>46133.665960648148</v>
@@ -27993,31 +28066,31 @@
     </row>
     <row r="18" spans="1:16" ht="25.5" customHeight="1">
       <c r="A18" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B18" t="s">
         <v>568</v>
       </c>
       <c r="C18" t="s">
-        <v>2321</v>
+        <v>2327</v>
       </c>
       <c r="D18" t="s">
-        <v>2322</v>
+        <v>2328</v>
       </c>
       <c r="E18" t="s">
-        <v>2323</v>
+        <v>2329</v>
       </c>
       <c r="F18" t="s">
-        <v>2324</v>
+        <v>2330</v>
       </c>
       <c r="G18" t="s">
-        <v>2325</v>
+        <v>2331</v>
       </c>
       <c r="J18" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K18" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L18" t="s">
         <v>574</v>
@@ -28026,7 +28099,7 @@
         <v>156</v>
       </c>
       <c r="N18" t="s">
-        <v>2326</v>
+        <v>2332</v>
       </c>
       <c r="O18" s="2">
         <v>46133.665960648148</v>
@@ -28037,40 +28110,40 @@
     </row>
     <row r="19" spans="1:16" ht="25.5" customHeight="1">
       <c r="A19" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B19" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C19" t="s">
-        <v>2327</v>
+        <v>2333</v>
       </c>
       <c r="D19" t="s">
-        <v>2328</v>
+        <v>2334</v>
       </c>
       <c r="E19" t="s">
-        <v>2329</v>
+        <v>2335</v>
       </c>
       <c r="F19" t="s">
-        <v>2330</v>
+        <v>2336</v>
       </c>
       <c r="G19" t="s">
-        <v>2331</v>
+        <v>2337</v>
       </c>
       <c r="J19" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K19" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L19" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M19" t="s">
         <v>53</v>
       </c>
       <c r="N19" t="s">
-        <v>2332</v>
+        <v>2338</v>
       </c>
       <c r="O19" s="2">
         <v>46133.665960648148</v>
@@ -28081,40 +28154,40 @@
     </row>
     <row r="20" spans="1:16" ht="25.5" customHeight="1">
       <c r="A20" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B20" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C20" t="s">
-        <v>2333</v>
+        <v>2339</v>
       </c>
       <c r="D20" t="s">
-        <v>2334</v>
+        <v>2340</v>
       </c>
       <c r="E20" t="s">
-        <v>2335</v>
+        <v>2341</v>
       </c>
       <c r="F20" t="s">
-        <v>2336</v>
+        <v>2342</v>
       </c>
       <c r="G20" t="s">
         <v>1709</v>
       </c>
       <c r="J20" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K20" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L20" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M20" t="s">
         <v>33</v>
       </c>
       <c r="N20" t="s">
-        <v>2337</v>
+        <v>2343</v>
       </c>
       <c r="O20" s="2">
         <v>46149.687719907408</v>
@@ -28125,40 +28198,40 @@
     </row>
     <row r="21" spans="1:16" ht="25.5" customHeight="1">
       <c r="A21" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B21" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C21" t="s">
-        <v>2338</v>
+        <v>2344</v>
       </c>
       <c r="D21" t="s">
-        <v>2339</v>
+        <v>2345</v>
       </c>
       <c r="E21" t="s">
-        <v>2340</v>
+        <v>2346</v>
       </c>
       <c r="F21" t="s">
-        <v>2341</v>
+        <v>2347</v>
       </c>
       <c r="G21" t="s">
         <v>1709</v>
       </c>
       <c r="J21" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K21" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L21" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M21" t="s">
         <v>42</v>
       </c>
       <c r="N21" t="s">
-        <v>2342</v>
+        <v>2348</v>
       </c>
       <c r="O21" s="2">
         <v>46149.629606481481</v>
@@ -28169,40 +28242,40 @@
     </row>
     <row r="22" spans="1:16" ht="25.5" customHeight="1">
       <c r="A22" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B22" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C22" t="s">
-        <v>2343</v>
+        <v>2349</v>
       </c>
       <c r="D22" t="s">
-        <v>2344</v>
+        <v>2350</v>
       </c>
       <c r="E22" t="s">
-        <v>2345</v>
+        <v>2351</v>
       </c>
       <c r="F22" t="s">
-        <v>2346</v>
+        <v>2352</v>
       </c>
       <c r="G22" t="s">
-        <v>2347</v>
+        <v>2353</v>
       </c>
       <c r="J22" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K22" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L22" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M22" t="s">
         <v>62</v>
       </c>
       <c r="N22" t="s">
-        <v>2348</v>
+        <v>2354</v>
       </c>
       <c r="O22" s="2">
         <v>46133.665960648148</v>
@@ -28213,40 +28286,40 @@
     </row>
     <row r="23" spans="1:16" ht="25.5" customHeight="1">
       <c r="A23" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B23" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C23" t="s">
-        <v>2349</v>
+        <v>2355</v>
       </c>
       <c r="D23" t="s">
-        <v>2350</v>
+        <v>2356</v>
       </c>
       <c r="E23" t="s">
-        <v>2351</v>
+        <v>2357</v>
       </c>
       <c r="F23" t="s">
-        <v>2352</v>
+        <v>2358</v>
       </c>
       <c r="G23" t="s">
         <v>1709</v>
       </c>
       <c r="J23" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K23" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L23" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M23" t="s">
         <v>69</v>
       </c>
       <c r="N23" t="s">
-        <v>2353</v>
+        <v>2359</v>
       </c>
       <c r="O23" s="2">
         <v>46133.665960648148</v>
@@ -28257,40 +28330,40 @@
     </row>
     <row r="24" spans="1:16" ht="25.5" customHeight="1">
       <c r="A24" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B24" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C24" t="s">
-        <v>2354</v>
+        <v>2360</v>
       </c>
       <c r="D24" t="s">
-        <v>2355</v>
+        <v>2361</v>
       </c>
       <c r="E24" t="s">
-        <v>2356</v>
+        <v>2362</v>
       </c>
       <c r="F24" t="s">
-        <v>2357</v>
+        <v>2363</v>
       </c>
       <c r="G24" t="s">
-        <v>2358</v>
+        <v>2364</v>
       </c>
       <c r="J24" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K24" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L24" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M24" t="s">
         <v>78</v>
       </c>
       <c r="N24" t="s">
-        <v>2359</v>
+        <v>2365</v>
       </c>
       <c r="O24" s="2">
         <v>46133.665960648148</v>
@@ -28301,40 +28374,40 @@
     </row>
     <row r="25" spans="1:16" ht="25.5" customHeight="1">
       <c r="A25" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B25" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C25" t="s">
-        <v>2360</v>
+        <v>2366</v>
       </c>
       <c r="D25" t="s">
-        <v>2361</v>
+        <v>2367</v>
       </c>
       <c r="E25" t="s">
-        <v>2362</v>
+        <v>2368</v>
       </c>
       <c r="F25" t="s">
-        <v>2363</v>
+        <v>2369</v>
       </c>
       <c r="G25" t="s">
-        <v>2364</v>
+        <v>2370</v>
       </c>
       <c r="J25" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K25" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L25" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M25" t="s">
         <v>85</v>
       </c>
       <c r="N25" t="s">
-        <v>2365</v>
+        <v>2371</v>
       </c>
       <c r="O25" s="2">
         <v>46133.665960648148</v>
@@ -28345,40 +28418,40 @@
     </row>
     <row r="26" spans="1:16" ht="25.5" customHeight="1">
       <c r="A26" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B26" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C26" t="s">
-        <v>2366</v>
+        <v>2372</v>
       </c>
       <c r="D26" t="s">
-        <v>2367</v>
+        <v>2373</v>
       </c>
       <c r="E26" t="s">
-        <v>2368</v>
+        <v>2374</v>
       </c>
       <c r="F26" t="s">
-        <v>2369</v>
+        <v>2375</v>
       </c>
       <c r="G26" t="s">
-        <v>2370</v>
+        <v>2376</v>
       </c>
       <c r="J26" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K26" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L26" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M26" t="s">
         <v>92</v>
       </c>
       <c r="N26" t="s">
-        <v>2371</v>
+        <v>2377</v>
       </c>
       <c r="O26" s="2">
         <v>46133.665960648148</v>
@@ -28389,40 +28462,40 @@
     </row>
     <row r="27" spans="1:16" ht="25.5" customHeight="1">
       <c r="A27" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B27" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C27" t="s">
-        <v>2372</v>
+        <v>2378</v>
       </c>
       <c r="D27" t="s">
-        <v>2373</v>
+        <v>2379</v>
       </c>
       <c r="E27" t="s">
-        <v>2374</v>
+        <v>2380</v>
       </c>
       <c r="F27" t="s">
-        <v>2375</v>
+        <v>2381</v>
       </c>
       <c r="G27" t="s">
         <v>1709</v>
       </c>
       <c r="J27" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K27" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L27" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M27" t="s">
         <v>99</v>
       </c>
       <c r="N27" t="s">
-        <v>2376</v>
+        <v>2382</v>
       </c>
       <c r="O27" s="2">
         <v>46133.665960648148</v>
@@ -28433,40 +28506,40 @@
     </row>
     <row r="28" spans="1:16" ht="25.5" customHeight="1">
       <c r="A28" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B28" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C28" t="s">
-        <v>2377</v>
+        <v>2383</v>
       </c>
       <c r="D28" t="s">
-        <v>2378</v>
+        <v>2384</v>
       </c>
       <c r="E28" t="s">
-        <v>2379</v>
+        <v>2385</v>
       </c>
       <c r="F28" t="s">
-        <v>2380</v>
+        <v>2386</v>
       </c>
       <c r="G28" t="s">
-        <v>2381</v>
+        <v>2387</v>
       </c>
       <c r="J28" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K28" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L28" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M28" t="s">
         <v>106</v>
       </c>
       <c r="N28" t="s">
-        <v>2382</v>
+        <v>2388</v>
       </c>
       <c r="O28" s="2">
         <v>46133.665960648148</v>
@@ -28477,40 +28550,40 @@
     </row>
     <row r="29" spans="1:16" ht="25.5" customHeight="1">
       <c r="A29" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B29" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C29" t="s">
-        <v>2383</v>
+        <v>2389</v>
       </c>
       <c r="D29" t="s">
-        <v>2384</v>
+        <v>2390</v>
       </c>
       <c r="E29" t="s">
-        <v>2385</v>
+        <v>2391</v>
       </c>
       <c r="F29" t="s">
-        <v>2386</v>
+        <v>2392</v>
       </c>
       <c r="G29" t="s">
-        <v>2387</v>
+        <v>2393</v>
       </c>
       <c r="J29" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K29" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L29" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M29" t="s">
         <v>113</v>
       </c>
       <c r="N29" t="s">
-        <v>2388</v>
+        <v>2394</v>
       </c>
       <c r="O29" s="2">
         <v>46133.665960648148</v>
@@ -28521,40 +28594,40 @@
     </row>
     <row r="30" spans="1:16" ht="25.5" customHeight="1">
       <c r="A30" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B30" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C30" t="s">
-        <v>2389</v>
+        <v>2395</v>
       </c>
       <c r="D30" t="s">
-        <v>2390</v>
+        <v>2396</v>
       </c>
       <c r="E30" t="s">
-        <v>2391</v>
+        <v>2397</v>
       </c>
       <c r="F30" t="s">
-        <v>2392</v>
+        <v>2398</v>
       </c>
       <c r="G30" t="s">
-        <v>2393</v>
+        <v>2399</v>
       </c>
       <c r="J30" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K30" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L30" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M30" t="s">
         <v>120</v>
       </c>
       <c r="N30" t="s">
-        <v>2394</v>
+        <v>2400</v>
       </c>
       <c r="O30" s="2">
         <v>46133.665960648148</v>
@@ -28565,40 +28638,40 @@
     </row>
     <row r="31" spans="1:16" ht="25.5" customHeight="1">
       <c r="A31" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B31" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C31" t="s">
-        <v>2395</v>
+        <v>2401</v>
       </c>
       <c r="D31" t="s">
-        <v>2396</v>
+        <v>2402</v>
       </c>
       <c r="E31" t="s">
-        <v>2397</v>
+        <v>2403</v>
       </c>
       <c r="F31" t="s">
-        <v>2398</v>
+        <v>2404</v>
       </c>
       <c r="G31" t="s">
-        <v>2399</v>
+        <v>2405</v>
       </c>
       <c r="J31" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K31" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L31" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M31" t="s">
         <v>127</v>
       </c>
       <c r="N31" t="s">
-        <v>2400</v>
+        <v>2406</v>
       </c>
       <c r="O31" s="2">
         <v>46224.754074074073</v>
@@ -28609,40 +28682,40 @@
     </row>
     <row r="32" spans="1:16" ht="25.5" customHeight="1">
       <c r="A32" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B32" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C32" t="s">
-        <v>2401</v>
+        <v>2407</v>
       </c>
       <c r="D32" t="s">
-        <v>2402</v>
+        <v>2408</v>
       </c>
       <c r="E32" t="s">
-        <v>2403</v>
+        <v>2409</v>
       </c>
       <c r="F32" t="s">
-        <v>2404</v>
+        <v>2410</v>
       </c>
       <c r="G32" t="s">
-        <v>2399</v>
+        <v>2405</v>
       </c>
       <c r="J32" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K32" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L32" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M32" t="s">
         <v>135</v>
       </c>
       <c r="N32" t="s">
-        <v>2405</v>
+        <v>2411</v>
       </c>
       <c r="O32" s="2">
         <v>46133.665960648148</v>
@@ -28653,40 +28726,40 @@
     </row>
     <row r="33" spans="1:16" ht="25.5" customHeight="1">
       <c r="A33" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B33" t="s">
-        <v>2406</v>
+        <v>2412</v>
       </c>
       <c r="C33" t="s">
-        <v>2407</v>
+        <v>2413</v>
       </c>
       <c r="D33" t="s">
-        <v>2408</v>
+        <v>2414</v>
       </c>
       <c r="E33" t="s">
-        <v>2409</v>
+        <v>2415</v>
       </c>
       <c r="F33" t="s">
-        <v>2410</v>
+        <v>2416</v>
       </c>
       <c r="G33" t="s">
-        <v>2411</v>
+        <v>2417</v>
       </c>
       <c r="J33" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K33" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L33" t="s">
-        <v>2412</v>
+        <v>2418</v>
       </c>
       <c r="M33" t="s">
         <v>53</v>
       </c>
       <c r="N33" t="s">
-        <v>2413</v>
+        <v>2419</v>
       </c>
       <c r="O33" s="2">
         <v>46133.665960648148</v>
@@ -28697,40 +28770,40 @@
     </row>
     <row r="34" spans="1:16" ht="25.5" customHeight="1">
       <c r="A34" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B34" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C34" t="s">
-        <v>2415</v>
+        <v>2421</v>
       </c>
       <c r="D34" t="s">
-        <v>2416</v>
+        <v>2422</v>
       </c>
       <c r="E34" t="s">
-        <v>2417</v>
+        <v>2423</v>
       </c>
       <c r="F34" t="s">
-        <v>2418</v>
+        <v>2424</v>
       </c>
       <c r="G34" t="s">
         <v>1709</v>
       </c>
       <c r="J34" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K34" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L34" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M34" t="s">
         <v>53</v>
       </c>
       <c r="N34" t="s">
-        <v>2420</v>
+        <v>2426</v>
       </c>
       <c r="O34" s="2">
         <v>46133.665960648148</v>
@@ -28741,40 +28814,40 @@
     </row>
     <row r="35" spans="1:16" ht="25.5" customHeight="1">
       <c r="A35" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B35" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C35" t="s">
-        <v>2421</v>
+        <v>2427</v>
       </c>
       <c r="D35" t="s">
-        <v>2422</v>
+        <v>2428</v>
       </c>
       <c r="E35" t="s">
-        <v>2423</v>
+        <v>2429</v>
       </c>
       <c r="F35" t="s">
-        <v>2424</v>
+        <v>2430</v>
       </c>
       <c r="G35" t="s">
         <v>1709</v>
       </c>
       <c r="J35" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K35" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L35" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M35" t="s">
         <v>33</v>
       </c>
       <c r="N35" t="s">
-        <v>2425</v>
+        <v>2431</v>
       </c>
       <c r="O35" s="2">
         <v>46149.631990740738</v>
@@ -28785,40 +28858,40 @@
     </row>
     <row r="36" spans="1:16" ht="25.5" customHeight="1">
       <c r="A36" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B36" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C36" t="s">
-        <v>2426</v>
+        <v>2432</v>
       </c>
       <c r="D36" t="s">
-        <v>2427</v>
+        <v>2433</v>
       </c>
       <c r="E36" t="s">
-        <v>2428</v>
+        <v>2434</v>
       </c>
       <c r="F36" t="s">
-        <v>2429</v>
+        <v>2435</v>
       </c>
       <c r="G36" t="s">
         <v>1709</v>
       </c>
       <c r="J36" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K36" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L36" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M36" t="s">
         <v>42</v>
       </c>
       <c r="N36" t="s">
-        <v>2430</v>
+        <v>2436</v>
       </c>
       <c r="O36" s="2">
         <v>46133.665960648148</v>
@@ -28829,40 +28902,40 @@
     </row>
     <row r="37" spans="1:16" ht="25.5" customHeight="1">
       <c r="A37" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B37" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C37" t="s">
-        <v>2431</v>
+        <v>2437</v>
       </c>
       <c r="D37" t="s">
-        <v>2432</v>
+        <v>2438</v>
       </c>
       <c r="E37" t="s">
-        <v>2433</v>
+        <v>2439</v>
       </c>
       <c r="F37" t="s">
-        <v>2434</v>
+        <v>2440</v>
       </c>
       <c r="G37" t="s">
         <v>1709</v>
       </c>
       <c r="J37" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K37" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L37" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M37" t="s">
         <v>62</v>
       </c>
       <c r="N37" t="s">
-        <v>2435</v>
+        <v>2441</v>
       </c>
       <c r="O37" s="2">
         <v>46133.665960648148</v>
@@ -28873,40 +28946,40 @@
     </row>
     <row r="38" spans="1:16" ht="25.5" customHeight="1">
       <c r="A38" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B38" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C38" t="s">
-        <v>2436</v>
+        <v>2442</v>
       </c>
       <c r="D38" t="s">
-        <v>2437</v>
+        <v>2443</v>
       </c>
       <c r="E38" t="s">
-        <v>2438</v>
+        <v>2444</v>
       </c>
       <c r="F38" t="s">
-        <v>2439</v>
+        <v>2445</v>
       </c>
       <c r="G38" t="s">
         <v>1709</v>
       </c>
       <c r="J38" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K38" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L38" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M38" t="s">
         <v>69</v>
       </c>
       <c r="N38" t="s">
-        <v>2440</v>
+        <v>2446</v>
       </c>
       <c r="O38" s="2">
         <v>46133.665960648148</v>
@@ -28917,43 +28990,43 @@
     </row>
     <row r="39" spans="1:16" ht="25.5" customHeight="1">
       <c r="A39" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B39" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C39" t="s">
-        <v>2441</v>
+        <v>2447</v>
       </c>
       <c r="D39" t="s">
-        <v>2442</v>
+        <v>2448</v>
       </c>
       <c r="E39" t="s">
-        <v>2443</v>
+        <v>2449</v>
       </c>
       <c r="F39" t="s">
-        <v>2444</v>
+        <v>2450</v>
       </c>
       <c r="G39" t="s">
         <v>1709</v>
       </c>
       <c r="J39" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K39" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L39" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M39" t="s">
         <v>78</v>
       </c>
       <c r="N39" t="s">
-        <v>2445</v>
+        <v>2451</v>
       </c>
       <c r="O39" s="2">
-        <v>46133.665960648148</v>
+        <v>46268.698229166665</v>
       </c>
       <c r="P39">
         <v>38</v>
@@ -28961,40 +29034,40 @@
     </row>
     <row r="40" spans="1:16" ht="25.5" customHeight="1">
       <c r="A40" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B40" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C40" t="s">
-        <v>2446</v>
+        <v>2452</v>
       </c>
       <c r="D40" t="s">
-        <v>2447</v>
+        <v>2453</v>
       </c>
       <c r="E40" t="s">
-        <v>2448</v>
+        <v>2454</v>
       </c>
       <c r="F40" t="s">
-        <v>2449</v>
+        <v>2455</v>
       </c>
       <c r="G40" t="s">
         <v>1709</v>
       </c>
       <c r="J40" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K40" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L40" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M40" t="s">
         <v>85</v>
       </c>
       <c r="N40" t="s">
-        <v>2450</v>
+        <v>2456</v>
       </c>
       <c r="O40" s="2">
         <v>46133.665960648148</v>
@@ -29005,40 +29078,40 @@
     </row>
     <row r="41" spans="1:16" ht="25.5" customHeight="1">
       <c r="A41" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B41" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C41" t="s">
-        <v>2451</v>
+        <v>2457</v>
       </c>
       <c r="D41" t="s">
-        <v>2452</v>
+        <v>2458</v>
       </c>
       <c r="E41" t="s">
-        <v>2453</v>
+        <v>2459</v>
       </c>
       <c r="F41" t="s">
-        <v>2454</v>
+        <v>2460</v>
       </c>
       <c r="G41" t="s">
         <v>1709</v>
       </c>
       <c r="J41" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K41" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L41" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M41" t="s">
         <v>92</v>
       </c>
       <c r="N41" t="s">
-        <v>2455</v>
+        <v>2461</v>
       </c>
       <c r="O41" s="2">
         <v>46133.665960648148</v>
@@ -29049,40 +29122,40 @@
     </row>
     <row r="42" spans="1:16" ht="25.5" customHeight="1">
       <c r="A42" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B42" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C42" t="s">
-        <v>2456</v>
+        <v>2462</v>
       </c>
       <c r="D42" t="s">
-        <v>2457</v>
+        <v>2463</v>
       </c>
       <c r="E42" t="s">
-        <v>2458</v>
+        <v>2464</v>
       </c>
       <c r="F42" t="s">
-        <v>2459</v>
+        <v>2465</v>
       </c>
       <c r="G42" t="s">
         <v>1709</v>
       </c>
       <c r="J42" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K42" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L42" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M42" t="s">
         <v>99</v>
       </c>
       <c r="N42" t="s">
-        <v>2460</v>
+        <v>2466</v>
       </c>
       <c r="O42" s="2">
         <v>46133.665960648148</v>
@@ -29093,40 +29166,40 @@
     </row>
     <row r="43" spans="1:16" ht="25.5" customHeight="1">
       <c r="A43" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B43" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C43" t="s">
-        <v>2461</v>
+        <v>2467</v>
       </c>
       <c r="D43" t="s">
-        <v>2462</v>
+        <v>2468</v>
       </c>
       <c r="E43" t="s">
-        <v>2463</v>
+        <v>2469</v>
       </c>
       <c r="F43" t="s">
-        <v>2464</v>
+        <v>2470</v>
       </c>
       <c r="G43" t="s">
         <v>1709</v>
       </c>
       <c r="J43" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K43" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L43" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M43" t="s">
         <v>106</v>
       </c>
       <c r="N43" t="s">
-        <v>2465</v>
+        <v>2471</v>
       </c>
       <c r="O43" s="2">
         <v>46133.665960648148</v>
@@ -29137,40 +29210,40 @@
     </row>
     <row r="44" spans="1:16" ht="25.5" customHeight="1">
       <c r="A44" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B44" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C44" t="s">
-        <v>2466</v>
+        <v>2472</v>
       </c>
       <c r="D44" t="s">
-        <v>2467</v>
+        <v>2473</v>
       </c>
       <c r="E44" t="s">
-        <v>2468</v>
+        <v>2474</v>
       </c>
       <c r="F44" t="s">
-        <v>2469</v>
+        <v>2475</v>
       </c>
       <c r="G44" t="s">
         <v>1709</v>
       </c>
       <c r="J44" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K44" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L44" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M44" t="s">
         <v>113</v>
       </c>
       <c r="N44" t="s">
-        <v>2470</v>
+        <v>2476</v>
       </c>
       <c r="O44" s="2">
         <v>46133.665960648148</v>
@@ -29181,40 +29254,40 @@
     </row>
     <row r="45" spans="1:16" ht="25.5" customHeight="1">
       <c r="A45" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B45" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C45" t="s">
-        <v>2471</v>
+        <v>2477</v>
       </c>
       <c r="D45" t="s">
-        <v>2472</v>
+        <v>2478</v>
       </c>
       <c r="E45" t="s">
-        <v>2473</v>
+        <v>2479</v>
       </c>
       <c r="F45" t="s">
-        <v>2474</v>
+        <v>2480</v>
       </c>
       <c r="G45" t="s">
         <v>1709</v>
       </c>
       <c r="J45" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K45" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L45" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M45" t="s">
         <v>120</v>
       </c>
       <c r="N45" t="s">
-        <v>2475</v>
+        <v>2481</v>
       </c>
       <c r="O45" s="2">
         <v>46133.665960648148</v>
@@ -29225,40 +29298,40 @@
     </row>
     <row r="46" spans="1:16" ht="25.5" customHeight="1">
       <c r="A46" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B46" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C46" t="s">
-        <v>2476</v>
+        <v>2482</v>
       </c>
       <c r="D46" t="s">
-        <v>2477</v>
+        <v>2483</v>
       </c>
       <c r="E46" t="s">
-        <v>2478</v>
+        <v>2484</v>
       </c>
       <c r="F46" t="s">
-        <v>2479</v>
+        <v>2485</v>
       </c>
       <c r="G46" t="s">
         <v>1709</v>
       </c>
       <c r="J46" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K46" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L46" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M46" t="s">
         <v>127</v>
       </c>
       <c r="N46" t="s">
-        <v>2480</v>
+        <v>2486</v>
       </c>
       <c r="O46" s="2">
         <v>46133.665960648148</v>
@@ -29269,40 +29342,40 @@
     </row>
     <row r="47" spans="1:16" ht="25.5" customHeight="1">
       <c r="A47" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B47" t="s">
-        <v>2481</v>
+        <v>2487</v>
       </c>
       <c r="C47" t="s">
-        <v>2482</v>
+        <v>2488</v>
       </c>
       <c r="D47" t="s">
-        <v>2483</v>
+        <v>2489</v>
       </c>
       <c r="E47" t="s">
-        <v>2484</v>
+        <v>2490</v>
       </c>
       <c r="F47" t="s">
-        <v>2485</v>
+        <v>2491</v>
       </c>
       <c r="G47" t="s">
         <v>1709</v>
       </c>
       <c r="J47" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K47" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L47" t="s">
-        <v>2486</v>
+        <v>2492</v>
       </c>
       <c r="M47" t="s">
         <v>53</v>
       </c>
       <c r="N47" t="s">
-        <v>2487</v>
+        <v>2493</v>
       </c>
       <c r="O47" s="2">
         <v>46133.665960648148</v>
@@ -29313,40 +29386,40 @@
     </row>
     <row r="48" spans="1:16" ht="25.5" customHeight="1">
       <c r="A48" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B48" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="C48" t="s">
-        <v>2488</v>
+        <v>2494</v>
       </c>
       <c r="D48" t="s">
-        <v>2489</v>
+        <v>2495</v>
       </c>
       <c r="E48" t="s">
-        <v>2490</v>
+        <v>2496</v>
       </c>
       <c r="F48" t="s">
-        <v>2491</v>
+        <v>2497</v>
       </c>
       <c r="G48" t="s">
         <v>1709</v>
       </c>
       <c r="J48" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K48" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L48" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="M48" t="s">
         <v>135</v>
       </c>
       <c r="N48" t="s">
-        <v>2492</v>
+        <v>2498</v>
       </c>
       <c r="O48" s="2">
         <v>46133.665960648148</v>
@@ -29357,40 +29430,40 @@
     </row>
     <row r="49" spans="1:16" ht="25.5" customHeight="1">
       <c r="A49" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B49" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="C49" t="s">
-        <v>2493</v>
+        <v>2499</v>
       </c>
       <c r="D49" t="s">
-        <v>2494</v>
+        <v>2500</v>
       </c>
       <c r="E49" t="s">
-        <v>2495</v>
+        <v>2501</v>
       </c>
       <c r="F49" t="s">
-        <v>2496</v>
+        <v>2502</v>
       </c>
       <c r="G49" t="s">
         <v>1709</v>
       </c>
       <c r="J49" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="K49" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L49" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="M49" t="s">
         <v>142</v>
       </c>
       <c r="N49" t="s">
-        <v>2497</v>
+        <v>2503</v>
       </c>
       <c r="O49" s="2">
         <v>46133.850208333337</v>
@@ -29401,28 +29474,28 @@
     </row>
     <row r="50" spans="1:16" ht="25.5" customHeight="1">
       <c r="A50" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B50" t="s">
         <v>1672</v>
       </c>
       <c r="C50" t="s">
-        <v>2498</v>
+        <v>2504</v>
       </c>
       <c r="D50" t="s">
-        <v>2499</v>
+        <v>2505</v>
       </c>
       <c r="E50" t="s">
-        <v>2500</v>
+        <v>2506</v>
       </c>
       <c r="F50" t="s">
-        <v>2501</v>
+        <v>2507</v>
       </c>
       <c r="G50" t="s">
-        <v>2502</v>
+        <v>2508</v>
       </c>
       <c r="K50" t="s">
-        <v>2245</v>
+        <v>2251</v>
       </c>
       <c r="L50" t="s">
         <v>1682</v>
@@ -29431,7 +29504,7 @@
         <v>53</v>
       </c>
       <c r="N50" t="s">
-        <v>2503</v>
+        <v>2509</v>
       </c>
       <c r="O50" s="2">
         <v>46205.764756944445</v>
@@ -29442,11 +29515,14 @@
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
-  <dataValidations count="2">
+  <dataValidations count="3">
     <dataValidation type="list" sqref="B2:B49" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"订阅/付费问题,访问问题,管理员联系方式,使用问题,找不到功能,代理问题"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J2:J49" xr:uid="{00000000-0002-0000-0300-000001000000}">
+    <dataValidation type="list" sqref="I2:I49" xr:uid="{00000000-0002-0000-0300-000001000000}">
+      <formula1>"1,2,3,4"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="J2:J49" xr:uid="{00000000-0002-0000-0300-000002000000}">
       <formula1>"end_user_only"</formula1>
     </dataValidation>
   </dataValidations>
@@ -29455,7 +29531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34E5E3ED-1179-49F5-BBFD-524FA091B344}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F8B8ED2E-F90E-4A66-878C-4F38F6D4D2A6}">
   <dimension ref="A1:J5"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -29470,22 +29546,22 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2504</v>
+        <v>2510</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2505</v>
+        <v>2511</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2506</v>
+        <v>2512</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>2507</v>
+        <v>2513</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2508</v>
+        <v>2514</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>2509</v>
+        <v>2515</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>14</v>
@@ -29496,31 +29572,31 @@
     </row>
     <row r="2" spans="1:10" ht="25.5" customHeight="1">
       <c r="A2" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B2" t="s">
-        <v>2510</v>
+        <v>2516</v>
       </c>
       <c r="C2" t="s">
-        <v>2511</v>
+        <v>2517</v>
       </c>
       <c r="D2" t="s">
-        <v>2512</v>
+        <v>2518</v>
       </c>
       <c r="E2" t="s">
-        <v>2513</v>
+        <v>2519</v>
       </c>
       <c r="F2" t="s">
-        <v>2514</v>
+        <v>2520</v>
       </c>
       <c r="G2" t="s">
-        <v>2515</v>
+        <v>2521</v>
       </c>
       <c r="H2" t="s">
-        <v>2516</v>
+        <v>2522</v>
       </c>
       <c r="I2" t="s">
-        <v>2517</v>
+        <v>2523</v>
       </c>
       <c r="J2" s="2">
         <v>46267.726979166669</v>
@@ -29528,31 +29604,31 @@
     </row>
     <row r="3" spans="1:10" ht="25.5" customHeight="1">
       <c r="A3" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B3" t="s">
-        <v>2510</v>
+        <v>2516</v>
       </c>
       <c r="C3" t="s">
-        <v>2518</v>
+        <v>2524</v>
       </c>
       <c r="D3" t="s">
-        <v>2519</v>
+        <v>2525</v>
       </c>
       <c r="E3" t="s">
-        <v>2520</v>
+        <v>2526</v>
       </c>
       <c r="F3" t="s">
-        <v>2521</v>
+        <v>2527</v>
       </c>
       <c r="G3" t="s">
-        <v>2522</v>
+        <v>2528</v>
       </c>
       <c r="H3" t="s">
-        <v>2523</v>
+        <v>2529</v>
       </c>
       <c r="I3" t="s">
-        <v>2524</v>
+        <v>2530</v>
       </c>
       <c r="J3" s="2">
         <v>46267.730069444442</v>
@@ -29560,31 +29636,31 @@
     </row>
     <row r="4" spans="1:10" ht="25.5" customHeight="1">
       <c r="A4" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B4" t="s">
-        <v>2510</v>
+        <v>2516</v>
       </c>
       <c r="C4" t="s">
-        <v>2525</v>
+        <v>2531</v>
       </c>
       <c r="D4" t="s">
-        <v>2526</v>
+        <v>2532</v>
       </c>
       <c r="E4" t="s">
-        <v>2527</v>
+        <v>2533</v>
       </c>
       <c r="F4" t="s">
-        <v>2528</v>
+        <v>2534</v>
       </c>
       <c r="G4" t="s">
-        <v>2515</v>
+        <v>2521</v>
       </c>
       <c r="H4" t="s">
-        <v>2529</v>
+        <v>2535</v>
       </c>
       <c r="I4" t="s">
-        <v>2530</v>
+        <v>2536</v>
       </c>
       <c r="J4" s="2">
         <v>46267.732592592591</v>
@@ -29592,31 +29668,31 @@
     </row>
     <row r="5" spans="1:10" ht="25.5" customHeight="1">
       <c r="A5" t="s">
-        <v>2239</v>
+        <v>2245</v>
       </c>
       <c r="B5" t="s">
-        <v>2510</v>
+        <v>2516</v>
       </c>
       <c r="C5" t="s">
-        <v>2531</v>
+        <v>2537</v>
       </c>
       <c r="D5" t="s">
-        <v>2532</v>
+        <v>2538</v>
       </c>
       <c r="E5" t="s">
-        <v>2533</v>
+        <v>2539</v>
       </c>
       <c r="F5" t="s">
-        <v>2534</v>
+        <v>2540</v>
       </c>
       <c r="G5" t="s">
-        <v>2515</v>
+        <v>2521</v>
       </c>
       <c r="H5" t="s">
-        <v>2535</v>
+        <v>2541</v>
       </c>
       <c r="I5" t="s">
-        <v>2536</v>
+        <v>2542</v>
       </c>
       <c r="J5" s="2">
         <v>46267.597395833334</v>
@@ -29629,7 +29705,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE9D16B2-7AFE-4856-8869-9F756D77AFD0}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7377E0AB-FFC7-4EEC-A87E-F1ACE58726A6}">
   <dimension ref="A1:H58"/>
   <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
@@ -29638,25 +29714,25 @@
   <sheetData>
     <row r="1" spans="1:8" ht="12.95" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>2537</v>
+        <v>2543</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2538</v>
+        <v>2544</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2505</v>
+        <v>2511</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>2506</v>
+        <v>2512</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>2507</v>
+        <v>2513</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>10</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>2539</v>
+        <v>2545</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>16</v>
@@ -29673,16 +29749,16 @@
         <v>1511</v>
       </c>
       <c r="D2" t="s">
-        <v>2540</v>
+        <v>2546</v>
       </c>
       <c r="E2" t="s">
-        <v>2541</v>
+        <v>2547</v>
       </c>
       <c r="F2" t="s">
         <v>31</v>
       </c>
       <c r="G2" t="s">
-        <v>2542</v>
+        <v>2548</v>
       </c>
       <c r="H2" s="2">
         <v>46133.665763888886</v>
@@ -29690,25 +29766,25 @@
     </row>
     <row r="3" spans="1:8" ht="25.5" customHeight="1">
       <c r="A3" t="s">
-        <v>1995</v>
+        <v>2001</v>
       </c>
       <c r="B3" t="s">
-        <v>2001</v>
+        <v>2007</v>
       </c>
       <c r="C3" t="s">
-        <v>2543</v>
+        <v>2549</v>
       </c>
       <c r="D3" t="s">
-        <v>2544</v>
+        <v>2550</v>
       </c>
       <c r="E3" t="s">
-        <v>2545</v>
+        <v>2551</v>
       </c>
       <c r="F3" t="s">
         <v>52</v>
       </c>
       <c r="G3" t="s">
-        <v>2546</v>
+        <v>2552</v>
       </c>
       <c r="H3" s="2">
         <v>46133.665763888886</v>
@@ -29722,19 +29798,19 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>2547</v>
+        <v>2553</v>
       </c>
       <c r="D4" t="s">
-        <v>2548</v>
+        <v>2554</v>
       </c>
       <c r="E4" t="s">
-        <v>2549</v>
+        <v>2555</v>
       </c>
       <c r="F4" t="s">
         <v>52</v>
       </c>
       <c r="G4" t="s">
-        <v>2550</v>
+        <v>2556</v>
       </c>
       <c r="H4" s="2">
         <v>46157.820347222223</v>
@@ -29748,19 +29824,19 @@
         <v>1287</v>
       </c>
       <c r="C5" t="s">
-        <v>2551</v>
+        <v>2557</v>
       </c>
       <c r="D5" t="s">
-        <v>2552</v>
+        <v>2558</v>
       </c>
       <c r="E5" t="s">
-        <v>2553</v>
+        <v>2559</v>
       </c>
       <c r="F5" t="s">
         <v>31</v>
       </c>
       <c r="G5" t="s">
-        <v>2554</v>
+        <v>2560</v>
       </c>
       <c r="H5" s="2">
         <v>46157.819201388891</v>
@@ -29774,19 +29850,19 @@
         <v>1590</v>
       </c>
       <c r="C6" t="s">
-        <v>2555</v>
+        <v>2561</v>
       </c>
       <c r="D6" t="s">
-        <v>2556</v>
+        <v>2562</v>
       </c>
       <c r="E6" t="s">
-        <v>2541</v>
+        <v>2547</v>
       </c>
       <c r="F6" t="s">
         <v>52</v>
       </c>
       <c r="G6" t="s">
-        <v>2557</v>
+        <v>2563</v>
       </c>
       <c r="H6" s="2">
         <v>46133.665763888886</v>
@@ -29800,19 +29876,19 @@
         <v>387</v>
       </c>
       <c r="C7" t="s">
-        <v>2558</v>
+        <v>2564</v>
       </c>
       <c r="D7" t="s">
-        <v>2559</v>
+        <v>2565</v>
       </c>
       <c r="E7" t="s">
-        <v>2560</v>
+        <v>2566</v>
       </c>
       <c r="F7" t="s">
         <v>31</v>
       </c>
       <c r="G7" t="s">
-        <v>2561</v>
+        <v>2567</v>
       </c>
       <c r="H7" s="2">
         <v>46133.665763888886</v>
@@ -29826,19 +29902,19 @@
         <v>351</v>
       </c>
       <c r="C8" t="s">
-        <v>2562</v>
+        <v>2568</v>
       </c>
       <c r="D8" t="s">
-        <v>2563</v>
+        <v>2569</v>
       </c>
       <c r="E8" t="s">
-        <v>2564</v>
+        <v>2570</v>
       </c>
       <c r="F8" t="s">
         <v>31</v>
       </c>
       <c r="G8" t="s">
-        <v>2565</v>
+        <v>2571</v>
       </c>
       <c r="H8" s="2">
         <v>46133.665763888886</v>
@@ -29852,19 +29928,19 @@
         <v>318</v>
       </c>
       <c r="C9" t="s">
+        <v>2572</v>
+      </c>
+      <c r="D9" t="s">
+        <v>2573</v>
+      </c>
+      <c r="E9" t="s">
         <v>2566</v>
-      </c>
-      <c r="D9" t="s">
-        <v>2567</v>
-      </c>
-      <c r="E9" t="s">
-        <v>2560</v>
       </c>
       <c r="F9" t="s">
         <v>31</v>
       </c>
       <c r="G9" t="s">
-        <v>2568</v>
+        <v>2574</v>
       </c>
       <c r="H9" s="2">
         <v>46133.665763888886</v>
@@ -29878,19 +29954,19 @@
         <v>574</v>
       </c>
       <c r="C10" t="s">
-        <v>2569</v>
+        <v>2575</v>
       </c>
       <c r="D10" t="s">
-        <v>2570</v>
+        <v>2576</v>
       </c>
       <c r="E10" t="s">
-        <v>2571</v>
+        <v>2577</v>
       </c>
       <c r="F10" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="G10" t="s">
-        <v>2572</v>
+        <v>2578</v>
       </c>
       <c r="H10" s="2">
         <v>46133.665763888886</v>
@@ -29898,25 +29974,25 @@
     </row>
     <row r="11" spans="1:8" ht="25.5" customHeight="1">
       <c r="A11" t="s">
-        <v>1946</v>
+        <v>1952</v>
       </c>
       <c r="B11" t="s">
-        <v>1952</v>
+        <v>1958</v>
       </c>
       <c r="C11" t="s">
-        <v>2573</v>
+        <v>2579</v>
       </c>
       <c r="D11" t="s">
-        <v>2574</v>
+        <v>2580</v>
       </c>
       <c r="E11" t="s">
-        <v>2575</v>
+        <v>2581</v>
       </c>
       <c r="F11" t="s">
         <v>31</v>
       </c>
       <c r="G11" t="s">
-        <v>2576</v>
+        <v>2582</v>
       </c>
       <c r="H11" s="2">
         <v>46133.665763888886</v>
@@ -29930,19 +30006,19 @@
         <v>1475</v>
       </c>
       <c r="C12" t="s">
-        <v>2577</v>
+        <v>2583</v>
       </c>
       <c r="D12" t="s">
-        <v>2578</v>
+        <v>2584</v>
       </c>
       <c r="E12" t="s">
-        <v>2579</v>
+        <v>2585</v>
       </c>
       <c r="F12" t="s">
         <v>52</v>
       </c>
       <c r="G12" t="s">
-        <v>2580</v>
+        <v>2586</v>
       </c>
       <c r="H12" s="2">
         <v>46133.665763888886</v>
@@ -29956,19 +30032,19 @@
         <v>405</v>
       </c>
       <c r="C13" t="s">
-        <v>2581</v>
+        <v>2587</v>
       </c>
       <c r="D13" t="s">
-        <v>2582</v>
+        <v>2588</v>
       </c>
       <c r="E13" t="s">
-        <v>2571</v>
+        <v>2577</v>
       </c>
       <c r="F13" t="s">
         <v>31</v>
       </c>
       <c r="G13" t="s">
-        <v>2583</v>
+        <v>2589</v>
       </c>
       <c r="H13" s="2">
         <v>46133.665763888886</v>
@@ -29982,19 +30058,19 @@
         <v>1125</v>
       </c>
       <c r="C14" t="s">
-        <v>2584</v>
+        <v>2590</v>
       </c>
       <c r="D14" t="s">
-        <v>2585</v>
+        <v>2591</v>
       </c>
       <c r="E14" t="s">
-        <v>2586</v>
+        <v>2592</v>
       </c>
       <c r="F14" t="s">
         <v>31</v>
       </c>
       <c r="G14" t="s">
-        <v>2587</v>
+        <v>2593</v>
       </c>
       <c r="H14" s="2">
         <v>46133.665763888886</v>
@@ -30002,25 +30078,25 @@
     </row>
     <row r="15" spans="1:8" ht="25.5" customHeight="1">
       <c r="A15" t="s">
-        <v>2024</v>
+        <v>2030</v>
       </c>
       <c r="B15" t="s">
-        <v>2032</v>
+        <v>2038</v>
       </c>
       <c r="C15" t="s">
-        <v>2588</v>
+        <v>2594</v>
       </c>
       <c r="D15" t="s">
-        <v>2589</v>
+        <v>2595</v>
       </c>
       <c r="E15" t="s">
-        <v>2590</v>
+        <v>2596</v>
       </c>
       <c r="F15" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="G15" t="s">
-        <v>2591</v>
+        <v>2597</v>
       </c>
       <c r="H15" s="2">
         <v>46133.665763888886</v>
@@ -30034,19 +30110,19 @@
         <v>1054</v>
       </c>
       <c r="C16" t="s">
-        <v>2592</v>
+        <v>2598</v>
       </c>
       <c r="D16" t="s">
-        <v>2593</v>
+        <v>2599</v>
       </c>
       <c r="E16" t="s">
-        <v>2594</v>
+        <v>2600</v>
       </c>
       <c r="F16" t="s">
         <v>52</v>
       </c>
       <c r="G16" t="s">
-        <v>2595</v>
+        <v>2601</v>
       </c>
       <c r="H16" s="2">
         <v>46133.665763888886</v>
@@ -30054,25 +30130,25 @@
     </row>
     <row r="17" spans="1:8" ht="25.5" customHeight="1">
       <c r="A17" t="s">
-        <v>2406</v>
+        <v>2412</v>
       </c>
       <c r="B17" t="s">
-        <v>2412</v>
+        <v>2418</v>
       </c>
       <c r="C17" t="s">
-        <v>2596</v>
+        <v>2602</v>
       </c>
       <c r="D17" t="s">
-        <v>2597</v>
+        <v>2603</v>
       </c>
       <c r="E17" t="s">
-        <v>2598</v>
+        <v>2604</v>
       </c>
       <c r="F17" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="G17" t="s">
-        <v>2599</v>
+        <v>2605</v>
       </c>
       <c r="H17" s="2">
         <v>46133.665763888886</v>
@@ -30086,19 +30162,19 @@
         <v>308</v>
       </c>
       <c r="C18" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D18" t="s">
+        <v>2607</v>
+      </c>
+      <c r="E18" t="s">
         <v>2600</v>
-      </c>
-      <c r="D18" t="s">
-        <v>2601</v>
-      </c>
-      <c r="E18" t="s">
-        <v>2594</v>
       </c>
       <c r="F18" t="s">
         <v>52</v>
       </c>
       <c r="G18" t="s">
-        <v>2602</v>
+        <v>2608</v>
       </c>
       <c r="H18" s="2">
         <v>46133.665763888886</v>
@@ -30112,19 +30188,19 @@
         <v>1190</v>
       </c>
       <c r="C19" t="s">
-        <v>2603</v>
+        <v>2609</v>
       </c>
       <c r="D19" t="s">
-        <v>2604</v>
+        <v>2610</v>
       </c>
       <c r="E19" t="s">
-        <v>2605</v>
+        <v>2611</v>
       </c>
       <c r="F19" t="s">
         <v>31</v>
       </c>
       <c r="G19" t="s">
-        <v>2606</v>
+        <v>2612</v>
       </c>
       <c r="H19" s="2">
         <v>46133.665763888886</v>
@@ -30138,19 +30214,19 @@
         <v>1154</v>
       </c>
       <c r="C20" t="s">
-        <v>2607</v>
+        <v>2613</v>
       </c>
       <c r="D20" t="s">
-        <v>2608</v>
+        <v>2614</v>
       </c>
       <c r="E20" t="s">
-        <v>2605</v>
+        <v>2611</v>
       </c>
       <c r="F20" t="s">
         <v>31</v>
       </c>
       <c r="G20" t="s">
-        <v>2609</v>
+        <v>2615</v>
       </c>
       <c r="H20" s="2">
         <v>46133.665763888886</v>
@@ -30164,19 +30240,19 @@
         <v>1199</v>
       </c>
       <c r="C21" t="s">
-        <v>2610</v>
+        <v>2616</v>
       </c>
       <c r="D21" t="s">
+        <v>2617</v>
+      </c>
+      <c r="E21" t="s">
         <v>2611</v>
-      </c>
-      <c r="E21" t="s">
-        <v>2605</v>
       </c>
       <c r="F21" t="s">
         <v>31</v>
       </c>
       <c r="G21" t="s">
-        <v>2612</v>
+        <v>2618</v>
       </c>
       <c r="H21" s="2">
         <v>46133.665763888886</v>
@@ -30190,19 +30266,19 @@
         <v>1179</v>
       </c>
       <c r="C22" t="s">
-        <v>2613</v>
+        <v>2619</v>
       </c>
       <c r="D22" t="s">
-        <v>2614</v>
+        <v>2620</v>
       </c>
       <c r="E22" t="s">
-        <v>2605</v>
+        <v>2611</v>
       </c>
       <c r="F22" t="s">
         <v>31</v>
       </c>
       <c r="G22" t="s">
-        <v>2615</v>
+        <v>2621</v>
       </c>
       <c r="H22" s="2">
         <v>46133.665763888886</v>
@@ -30216,19 +30292,19 @@
         <v>910</v>
       </c>
       <c r="C23" t="s">
-        <v>2616</v>
+        <v>2622</v>
       </c>
       <c r="D23" t="s">
-        <v>2617</v>
+        <v>2623</v>
       </c>
       <c r="E23" t="s">
-        <v>2605</v>
+        <v>2611</v>
       </c>
       <c r="F23" t="s">
         <v>31</v>
       </c>
       <c r="G23" t="s">
-        <v>2618</v>
+        <v>2624</v>
       </c>
       <c r="H23" s="2">
         <v>46133.665763888886</v>
@@ -30242,19 +30318,19 @@
         <v>1062</v>
       </c>
       <c r="C24" t="s">
-        <v>2619</v>
+        <v>2625</v>
       </c>
       <c r="D24" t="s">
-        <v>2620</v>
+        <v>2626</v>
       </c>
       <c r="E24" t="s">
-        <v>2605</v>
+        <v>2611</v>
       </c>
       <c r="F24" t="s">
         <v>31</v>
       </c>
       <c r="G24" t="s">
-        <v>2621</v>
+        <v>2627</v>
       </c>
       <c r="H24" s="2">
         <v>46133.665763888886</v>
@@ -30268,19 +30344,19 @@
         <v>592</v>
       </c>
       <c r="C25" t="s">
-        <v>2622</v>
+        <v>2628</v>
       </c>
       <c r="D25" t="s">
-        <v>2623</v>
+        <v>2629</v>
       </c>
       <c r="E25" t="s">
-        <v>2624</v>
+        <v>2630</v>
       </c>
       <c r="F25" t="s">
         <v>52</v>
       </c>
       <c r="G25" t="s">
-        <v>2625</v>
+        <v>2631</v>
       </c>
       <c r="H25" s="2">
         <v>46133.665763888886</v>
@@ -30294,19 +30370,19 @@
         <v>1023</v>
       </c>
       <c r="C26" t="s">
-        <v>2626</v>
+        <v>2632</v>
       </c>
       <c r="D26" t="s">
-        <v>2627</v>
+        <v>2633</v>
       </c>
       <c r="E26" t="s">
-        <v>2628</v>
+        <v>2634</v>
       </c>
       <c r="F26" t="s">
         <v>52</v>
       </c>
       <c r="G26" t="s">
-        <v>2629</v>
+        <v>2635</v>
       </c>
       <c r="H26" s="2">
         <v>46133.665763888886</v>
@@ -30320,19 +30396,19 @@
         <v>1073</v>
       </c>
       <c r="C27" t="s">
-        <v>2630</v>
+        <v>2636</v>
       </c>
       <c r="D27" t="s">
-        <v>2631</v>
+        <v>2637</v>
       </c>
       <c r="E27" t="s">
-        <v>2628</v>
+        <v>2634</v>
       </c>
       <c r="F27" t="s">
         <v>31</v>
       </c>
       <c r="G27" t="s">
-        <v>2632</v>
+        <v>2638</v>
       </c>
       <c r="H27" s="2">
         <v>46133.665763888886</v>
@@ -30346,19 +30422,19 @@
         <v>1573</v>
       </c>
       <c r="C28" t="s">
-        <v>2633</v>
+        <v>2639</v>
       </c>
       <c r="D28" t="s">
-        <v>2634</v>
+        <v>2640</v>
       </c>
       <c r="E28" t="s">
-        <v>2541</v>
+        <v>2547</v>
       </c>
       <c r="F28" t="s">
         <v>52</v>
       </c>
       <c r="G28" t="s">
-        <v>2635</v>
+        <v>2641</v>
       </c>
       <c r="H28" s="2">
         <v>46133.665763888886</v>
@@ -30372,19 +30448,19 @@
         <v>340</v>
       </c>
       <c r="C29" t="s">
-        <v>2636</v>
+        <v>2642</v>
       </c>
       <c r="D29" t="s">
-        <v>2637</v>
+        <v>2643</v>
       </c>
       <c r="E29" t="s">
-        <v>2605</v>
+        <v>2611</v>
       </c>
       <c r="F29" t="s">
         <v>52</v>
       </c>
       <c r="G29" t="s">
-        <v>2638</v>
+        <v>2644</v>
       </c>
       <c r="H29" s="2">
         <v>46133.665763888886</v>
@@ -30398,19 +30474,19 @@
         <v>1372</v>
       </c>
       <c r="C30" t="s">
-        <v>2639</v>
+        <v>2645</v>
       </c>
       <c r="D30" t="s">
-        <v>2640</v>
+        <v>2646</v>
       </c>
       <c r="E30" t="s">
-        <v>2641</v>
+        <v>2647</v>
       </c>
       <c r="F30" t="s">
         <v>31</v>
       </c>
       <c r="G30" t="s">
-        <v>2642</v>
+        <v>2648</v>
       </c>
       <c r="H30" s="2">
         <v>46133.665763888886</v>
@@ -30424,19 +30500,19 @@
         <v>298</v>
       </c>
       <c r="C31" t="s">
-        <v>2643</v>
+        <v>2649</v>
       </c>
       <c r="D31" t="s">
-        <v>2644</v>
+        <v>2650</v>
       </c>
       <c r="E31" t="s">
-        <v>2645</v>
+        <v>2651</v>
       </c>
       <c r="F31" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="G31" t="s">
-        <v>2646</v>
+        <v>2652</v>
       </c>
       <c r="H31" s="2">
         <v>46133.665763888886</v>
@@ -30450,19 +30526,19 @@
         <v>1423</v>
       </c>
       <c r="C32" t="s">
+        <v>2653</v>
+      </c>
+      <c r="D32" t="s">
+        <v>2654</v>
+      </c>
+      <c r="E32" t="s">
         <v>2647</v>
-      </c>
-      <c r="D32" t="s">
-        <v>2648</v>
-      </c>
-      <c r="E32" t="s">
-        <v>2641</v>
       </c>
       <c r="F32" t="s">
         <v>31</v>
       </c>
       <c r="G32" t="s">
-        <v>2649</v>
+        <v>2655</v>
       </c>
       <c r="H32" s="2">
         <v>46133.665763888886</v>
@@ -30476,19 +30552,19 @@
         <v>1225</v>
       </c>
       <c r="C33" t="s">
-        <v>2650</v>
+        <v>2656</v>
       </c>
       <c r="D33" t="s">
-        <v>2651</v>
+        <v>2657</v>
       </c>
       <c r="E33" t="s">
-        <v>2579</v>
+        <v>2585</v>
       </c>
       <c r="F33" t="s">
         <v>52</v>
       </c>
       <c r="G33" t="s">
-        <v>2652</v>
+        <v>2658</v>
       </c>
       <c r="H33" s="2">
         <v>46133.665763888886</v>
@@ -30496,25 +30572,25 @@
     </row>
     <row r="34" spans="1:8" ht="25.5" customHeight="1">
       <c r="A34" t="s">
-        <v>2414</v>
+        <v>2420</v>
       </c>
       <c r="B34" t="s">
-        <v>2419</v>
+        <v>2425</v>
       </c>
       <c r="C34" t="s">
-        <v>2653</v>
+        <v>2659</v>
       </c>
       <c r="D34" t="s">
-        <v>2654</v>
+        <v>2660</v>
       </c>
       <c r="E34" t="s">
-        <v>2579</v>
+        <v>2585</v>
       </c>
       <c r="F34" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="G34" t="s">
-        <v>2655</v>
+        <v>2661</v>
       </c>
       <c r="H34" s="2">
         <v>46133.665763888886</v>
@@ -30528,19 +30604,19 @@
         <v>1163</v>
       </c>
       <c r="C35" t="s">
-        <v>2656</v>
+        <v>2662</v>
       </c>
       <c r="D35" t="s">
-        <v>2657</v>
+        <v>2663</v>
       </c>
       <c r="E35" t="s">
-        <v>2658</v>
+        <v>2664</v>
       </c>
       <c r="F35" t="s">
         <v>31</v>
       </c>
       <c r="G35" t="s">
-        <v>2659</v>
+        <v>2665</v>
       </c>
       <c r="H35" s="2">
         <v>46133.665763888886</v>
@@ -30554,19 +30630,19 @@
         <v>1502</v>
       </c>
       <c r="C36" t="s">
-        <v>2660</v>
+        <v>2666</v>
       </c>
       <c r="D36" t="s">
-        <v>2661</v>
+        <v>2667</v>
       </c>
       <c r="E36" t="s">
-        <v>2541</v>
+        <v>2547</v>
       </c>
       <c r="F36" t="s">
         <v>52</v>
       </c>
       <c r="G36" t="s">
-        <v>2662</v>
+        <v>2668</v>
       </c>
       <c r="H36" s="2">
         <v>46133.665763888886</v>
@@ -30580,19 +30656,19 @@
         <v>499</v>
       </c>
       <c r="C37" t="s">
-        <v>2663</v>
+        <v>2669</v>
       </c>
       <c r="D37" t="s">
-        <v>2664</v>
+        <v>2670</v>
       </c>
       <c r="E37" t="s">
-        <v>2571</v>
+        <v>2577</v>
       </c>
       <c r="F37" t="s">
         <v>31</v>
       </c>
       <c r="G37" t="s">
-        <v>2665</v>
+        <v>2671</v>
       </c>
       <c r="H37" s="2">
         <v>46133.665763888886</v>
@@ -30606,19 +30682,19 @@
         <v>476</v>
       </c>
       <c r="C38" t="s">
-        <v>2666</v>
+        <v>2672</v>
       </c>
       <c r="D38" t="s">
-        <v>2667</v>
+        <v>2673</v>
       </c>
       <c r="E38" t="s">
-        <v>2571</v>
+        <v>2577</v>
       </c>
       <c r="F38" t="s">
         <v>31</v>
       </c>
       <c r="G38" t="s">
-        <v>2668</v>
+        <v>2674</v>
       </c>
       <c r="H38" s="2">
         <v>46133.665763888886</v>
@@ -30632,19 +30708,19 @@
         <v>485</v>
       </c>
       <c r="C39" t="s">
-        <v>2669</v>
+        <v>2675</v>
       </c>
       <c r="D39" t="s">
-        <v>2670</v>
+        <v>2676</v>
       </c>
       <c r="E39" t="s">
-        <v>2571</v>
+        <v>2577</v>
       </c>
       <c r="F39" t="s">
         <v>31</v>
       </c>
       <c r="G39" t="s">
-        <v>2671</v>
+        <v>2677</v>
       </c>
       <c r="H39" s="2">
         <v>46133.665763888886</v>
@@ -30658,19 +30734,19 @@
         <v>1447</v>
       </c>
       <c r="C40" t="s">
-        <v>2672</v>
+        <v>2678</v>
       </c>
       <c r="D40" t="s">
-        <v>2673</v>
+        <v>2679</v>
       </c>
       <c r="E40" t="s">
-        <v>2553</v>
+        <v>2559</v>
       </c>
       <c r="F40" t="s">
         <v>31</v>
       </c>
       <c r="G40" t="s">
-        <v>2674</v>
+        <v>2680</v>
       </c>
       <c r="H40" s="2">
         <v>46133.665763888886</v>
@@ -30678,25 +30754,25 @@
     </row>
     <row r="41" spans="1:8" ht="25.5" customHeight="1">
       <c r="A41" t="s">
-        <v>2675</v>
+        <v>2681</v>
       </c>
       <c r="B41" t="s">
-        <v>2676</v>
+        <v>2682</v>
       </c>
       <c r="C41" t="s">
-        <v>2677</v>
+        <v>2683</v>
       </c>
       <c r="D41" t="s">
-        <v>2678</v>
+        <v>2684</v>
       </c>
       <c r="E41" t="s">
-        <v>2679</v>
+        <v>2685</v>
       </c>
       <c r="F41" t="s">
         <v>52</v>
       </c>
       <c r="G41" t="s">
-        <v>2680</v>
+        <v>2686</v>
       </c>
       <c r="H41" s="2">
         <v>46133.665763888886</v>
@@ -30710,19 +30786,19 @@
         <v>1269</v>
       </c>
       <c r="C42" t="s">
-        <v>2681</v>
+        <v>2687</v>
       </c>
       <c r="D42" t="s">
-        <v>2682</v>
+        <v>2688</v>
       </c>
       <c r="E42" t="s">
-        <v>2594</v>
+        <v>2600</v>
       </c>
       <c r="F42" t="s">
         <v>52</v>
       </c>
       <c r="G42" t="s">
-        <v>2683</v>
+        <v>2689</v>
       </c>
       <c r="H42" s="2">
         <v>46133.665763888886</v>
@@ -30730,25 +30806,25 @@
     </row>
     <row r="43" spans="1:8" ht="25.5" customHeight="1">
       <c r="A43" t="s">
-        <v>2083</v>
+        <v>2089</v>
       </c>
       <c r="B43" t="s">
-        <v>2089</v>
+        <v>2095</v>
       </c>
       <c r="C43" t="s">
-        <v>2684</v>
+        <v>2690</v>
       </c>
       <c r="D43" t="s">
+        <v>2691</v>
+      </c>
+      <c r="E43" t="s">
         <v>2685</v>
       </c>
-      <c r="E43" t="s">
-        <v>2679</v>
-      </c>
       <c r="F43" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="G43" t="s">
-        <v>2686</v>
+        <v>2692</v>
       </c>
       <c r="H43" s="2">
         <v>46133.665763888886</v>
@@ -30762,19 +30838,19 @@
         <v>404</v>
       </c>
       <c r="C44" t="s">
-        <v>2687</v>
+        <v>2693</v>
       </c>
       <c r="D44" t="s">
-        <v>2688</v>
+        <v>2694</v>
       </c>
       <c r="E44" t="s">
-        <v>2571</v>
+        <v>2577</v>
       </c>
       <c r="F44" t="s">
         <v>31</v>
       </c>
       <c r="G44" t="s">
-        <v>2689</v>
+        <v>2695</v>
       </c>
       <c r="H44" s="2">
         <v>46133.665763888886</v>
@@ -30788,19 +30864,19 @@
         <v>1107</v>
       </c>
       <c r="C45" t="s">
-        <v>2690</v>
+        <v>2696</v>
       </c>
       <c r="D45" t="s">
-        <v>2691</v>
+        <v>2697</v>
       </c>
       <c r="E45" t="s">
-        <v>2692</v>
+        <v>2698</v>
       </c>
       <c r="F45" t="s">
         <v>52</v>
       </c>
       <c r="G45" t="s">
-        <v>2693</v>
+        <v>2699</v>
       </c>
       <c r="H45" s="2">
         <v>46133.665763888886</v>
@@ -30814,19 +30890,19 @@
         <v>870</v>
       </c>
       <c r="C46" t="s">
-        <v>2694</v>
+        <v>2700</v>
       </c>
       <c r="D46" t="s">
-        <v>2695</v>
+        <v>2701</v>
       </c>
       <c r="E46" t="s">
-        <v>2696</v>
+        <v>2702</v>
       </c>
       <c r="F46" t="s">
         <v>31</v>
       </c>
       <c r="G46" t="s">
-        <v>2697</v>
+        <v>2703</v>
       </c>
       <c r="H46" s="2">
         <v>46133.665763888886</v>
@@ -30834,25 +30910,25 @@
     </row>
     <row r="47" spans="1:8" ht="25.5" customHeight="1">
       <c r="A47" t="s">
-        <v>2481</v>
+        <v>2487</v>
       </c>
       <c r="B47" t="s">
-        <v>2486</v>
+        <v>2492</v>
       </c>
       <c r="C47" t="s">
-        <v>2698</v>
+        <v>2704</v>
       </c>
       <c r="D47" t="s">
-        <v>2699</v>
+        <v>2705</v>
       </c>
       <c r="E47" t="s">
-        <v>2579</v>
+        <v>2585</v>
       </c>
       <c r="F47" t="s">
-        <v>2244</v>
+        <v>2250</v>
       </c>
       <c r="G47" t="s">
-        <v>2700</v>
+        <v>2706</v>
       </c>
       <c r="H47" s="2">
         <v>46133.665763888886</v>
@@ -30866,19 +30942,19 @@
         <v>522</v>
       </c>
       <c r="C48" t="s">
-        <v>2701</v>
+        <v>2707</v>
       </c>
       <c r="D48" t="s">
-        <v>2702</v>
+        <v>2708</v>
       </c>
       <c r="E48" t="s">
-        <v>2571</v>
+        <v>2577</v>
       </c>
       <c r="F48" t="s">
         <v>31</v>
       </c>
       <c r="G48" t="s">
-        <v>2703</v>
+        <v>2709</v>
       </c>
       <c r="H48" s="2">
         <v>46133.665763888886</v>
@@ -30892,19 +30968,19 @@
         <v>625</v>
       </c>
       <c r="C49" t="s">
-        <v>2704</v>
+        <v>2710</v>
       </c>
       <c r="D49" t="s">
-        <v>2705</v>
+        <v>2711</v>
       </c>
       <c r="E49" t="s">
-        <v>2586</v>
+        <v>2592</v>
       </c>
       <c r="F49" t="s">
         <v>52</v>
       </c>
       <c r="G49" t="s">
-        <v>2706</v>
+        <v>2712</v>
       </c>
       <c r="H49" s="2">
         <v>46133.665763888886</v>
@@ -30918,19 +30994,19 @@
         <v>1682</v>
       </c>
       <c r="C50" t="s">
-        <v>2707</v>
+        <v>2713</v>
       </c>
       <c r="D50" t="s">
-        <v>2708</v>
+        <v>2714</v>
       </c>
       <c r="E50" t="s">
-        <v>2709</v>
+        <v>2715</v>
       </c>
       <c r="F50" t="s">
         <v>52</v>
       </c>
       <c r="G50" t="s">
-        <v>2710</v>
+        <v>2716</v>
       </c>
       <c r="H50" s="2">
         <v>46133.665763888886</v>
@@ -30944,19 +31020,19 @@
         <v>1710</v>
       </c>
       <c r="C51" t="s">
-        <v>2711</v>
+        <v>2717</v>
       </c>
       <c r="D51" t="s">
-        <v>2712</v>
+        <v>2718</v>
       </c>
       <c r="E51" t="s">
-        <v>2713</v>
+        <v>2719</v>
       </c>
       <c r="F51" t="s">
         <v>52</v>
       </c>
       <c r="G51" t="s">
-        <v>2714</v>
+        <v>2720</v>
       </c>
       <c r="H51" s="2">
         <v>46133.665763888886</v>
@@ -30970,19 +31046,19 @@
         <v>1777</v>
       </c>
       <c r="C52" t="s">
-        <v>2715</v>
+        <v>2721</v>
       </c>
       <c r="D52" t="s">
-        <v>2716</v>
+        <v>2722</v>
       </c>
       <c r="E52" t="s">
-        <v>2717</v>
+        <v>2723</v>
       </c>
       <c r="F52" t="s">
         <v>52</v>
       </c>
       <c r="G52" t="s">
-        <v>2718</v>
+        <v>2724</v>
       </c>
       <c r="H52" s="2">
         <v>46133.665763888886</v>
@@ -30990,25 +31066,25 @@
     </row>
     <row r="53" spans="1:8" ht="25.5" customHeight="1">
       <c r="A53" t="s">
-        <v>1912</v>
+        <v>1918</v>
       </c>
       <c r="B53" t="s">
-        <v>1919</v>
+        <v>1925</v>
       </c>
       <c r="C53" t="s">
-        <v>2719</v>
+        <v>2725</v>
       </c>
       <c r="D53" t="s">
-        <v>2720</v>
+        <v>2726</v>
       </c>
       <c r="E53" t="s">
-        <v>2721</v>
+        <v>2727</v>
       </c>
       <c r="F53" t="s">
         <v>52</v>
       </c>
       <c r="G53" t="s">
-        <v>2722</v>
+        <v>2728</v>
       </c>
       <c r="H53" s="2">
         <v>46133.665763888886</v>
@@ -31022,19 +31098,19 @@
         <v>1858</v>
       </c>
       <c r="C54" t="s">
-        <v>2723</v>
+        <v>2729</v>
       </c>
       <c r="D54" t="s">
-        <v>2724</v>
+        <v>2730</v>
       </c>
       <c r="E54" t="s">
-        <v>2725</v>
+        <v>2731</v>
       </c>
       <c r="F54" t="s">
         <v>52</v>
       </c>
       <c r="G54" t="s">
-        <v>2725</v>
+        <v>2731</v>
       </c>
       <c r="H54" s="2">
         <v>46133.665763888886</v>
@@ -31042,25 +31118,25 @@
     </row>
     <row r="55" spans="1:8" ht="25.5" customHeight="1">
       <c r="A55" t="s">
-        <v>1966</v>
+        <v>1972</v>
       </c>
       <c r="B55" t="s">
-        <v>1972</v>
+        <v>1978</v>
       </c>
       <c r="C55" t="s">
-        <v>2726</v>
+        <v>2732</v>
       </c>
       <c r="D55" t="s">
-        <v>2727</v>
+        <v>2733</v>
       </c>
       <c r="E55" t="s">
-        <v>2728</v>
+        <v>2734</v>
       </c>
       <c r="F55" t="s">
         <v>52</v>
       </c>
       <c r="G55" t="s">
-        <v>2728</v>
+        <v>2734</v>
       </c>
       <c r="H55" s="2">
         <v>46133.665763888886</v>
@@ -31074,19 +31150,19 @@
         <v>1885</v>
       </c>
       <c r="C56" t="s">
-        <v>2729</v>
+        <v>2735</v>
       </c>
       <c r="D56" t="s">
-        <v>2730</v>
+        <v>2736</v>
       </c>
       <c r="E56" t="s">
-        <v>2731</v>
+        <v>2737</v>
       </c>
       <c r="F56" t="s">
         <v>52</v>
       </c>
       <c r="G56" t="s">
-        <v>2732</v>
+        <v>2738</v>
       </c>
       <c r="H56" s="2">
         <v>46133.665763888886</v>
@@ -31100,19 +31176,19 @@
         <v>1484</v>
       </c>
       <c r="C57" t="s">
-        <v>2733</v>
+        <v>2739</v>
       </c>
       <c r="D57" t="s">
-        <v>2734</v>
+        <v>2740</v>
       </c>
       <c r="E57" t="s">
-        <v>2735</v>
+        <v>2741</v>
       </c>
       <c r="F57" t="s">
         <v>52</v>
       </c>
       <c r="G57" t="s">
-        <v>2736</v>
+        <v>2742</v>
       </c>
       <c r="H57" s="2">
         <v>46133.665763888886</v>
@@ -31126,19 +31202,19 @@
         <v>1605</v>
       </c>
       <c r="C58" t="s">
-        <v>2737</v>
+        <v>2743</v>
       </c>
       <c r="D58" t="s">
-        <v>2738</v>
+        <v>2744</v>
       </c>
       <c r="E58" t="s">
-        <v>2541</v>
+        <v>2547</v>
       </c>
       <c r="F58" t="s">
         <v>31</v>
       </c>
       <c r="G58" t="s">
-        <v>2739</v>
+        <v>2745</v>
       </c>
       <c r="H58" s="2">
         <v>46202.713923611111</v>
